--- a/W13/analysis/W13_growth_by_settlement.xlsx
+++ b/W13/analysis/W13_growth_by_settlement.xlsx
@@ -555,19 +555,19 @@
         <v>34139</v>
       </c>
       <c r="N2" t="n">
-        <v>2222.4</v>
+        <v>2030</v>
       </c>
       <c r="O2" t="n">
-        <v>2555</v>
+        <v>2362.6</v>
       </c>
       <c r="P2" t="n">
-        <v>4339.3</v>
+        <v>4146.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="R2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
     </row>
     <row r="3">
@@ -613,19 +613,19 @@
         <v>7846</v>
       </c>
       <c r="N3" t="n">
-        <v>634.9</v>
+        <v>480.9</v>
       </c>
       <c r="O3" t="n">
-        <v>711.3</v>
+        <v>557.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1121.4</v>
+        <v>967.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
     </row>
     <row r="4">
@@ -671,19 +671,19 @@
         <v>1383</v>
       </c>
       <c r="N4" t="n">
-        <v>109.3</v>
+        <v>82.2</v>
       </c>
       <c r="O4" t="n">
-        <v>122.8</v>
+        <v>95.7</v>
       </c>
       <c r="P4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="R4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
     </row>
     <row r="5">
@@ -729,19 +729,19 @@
         <v>30815</v>
       </c>
       <c r="N5" t="n">
-        <v>2247</v>
+        <v>1832.3</v>
       </c>
       <c r="O5" t="n">
-        <v>2547.2</v>
+        <v>2132.5</v>
       </c>
       <c r="P5" t="n">
-        <v>4157.8</v>
+        <v>3743</v>
       </c>
       <c r="Q5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="R5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
     </row>
     <row r="6">
@@ -787,19 +787,19 @@
         <v>13115</v>
       </c>
       <c r="N6" t="n">
-        <v>810.1</v>
+        <v>779.8</v>
       </c>
       <c r="O6" t="n">
-        <v>937.8</v>
+        <v>907.6</v>
       </c>
       <c r="P6" t="n">
-        <v>1623.3</v>
+        <v>1593</v>
       </c>
       <c r="Q6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="R6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
     </row>
     <row r="7">
@@ -845,19 +845,19 @@
         <v>1855</v>
       </c>
       <c r="N7" t="n">
-        <v>146.7</v>
+        <v>110.3</v>
       </c>
       <c r="O7" t="n">
-        <v>164.8</v>
+        <v>128.4</v>
       </c>
       <c r="P7" t="n">
-        <v>337.2</v>
+        <v>300.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>852.4</v>
+        <v>816</v>
       </c>
       <c r="R7" t="n">
-        <v>852.4</v>
+        <v>816</v>
       </c>
     </row>
     <row r="8">
@@ -903,19 +903,19 @@
         <v>3963</v>
       </c>
       <c r="N8" t="n">
-        <v>313.5</v>
+        <v>235.7</v>
       </c>
       <c r="O8" t="n">
-        <v>352.1</v>
+        <v>274.3</v>
       </c>
       <c r="P8" t="n">
-        <v>559.2</v>
+        <v>481.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
     </row>
     <row r="9">
@@ -961,19 +961,19 @@
         <v>7731</v>
       </c>
       <c r="N9" t="n">
-        <v>477.5</v>
+        <v>459.7</v>
       </c>
       <c r="O9" t="n">
-        <v>553.5</v>
+        <v>535.7</v>
       </c>
       <c r="P9" t="n">
-        <v>961.1</v>
+        <v>943.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>2414</v>
+        <v>2396.2</v>
       </c>
       <c r="R9" t="n">
-        <v>2414</v>
+        <v>2396.2</v>
       </c>
     </row>
     <row r="10">
@@ -1019,19 +1019,19 @@
         <v>1048</v>
       </c>
       <c r="N10" t="n">
-        <v>102.2</v>
+        <v>81.7</v>
       </c>
       <c r="O10" t="n">
-        <v>112.4</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>167.2</v>
+        <v>146.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
       <c r="R10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
     </row>
     <row r="11">
@@ -1077,19 +1077,19 @@
         <v>645</v>
       </c>
       <c r="N11" t="n">
-        <v>51</v>
+        <v>38.4</v>
       </c>
       <c r="O11" t="n">
-        <v>57.3</v>
+        <v>44.7</v>
       </c>
       <c r="P11" t="n">
-        <v>158.5</v>
+        <v>145.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="R11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
     </row>
     <row r="12">
@@ -1135,19 +1135,19 @@
         <v>1694</v>
       </c>
       <c r="N12" t="n">
-        <v>133.9</v>
+        <v>100.7</v>
       </c>
       <c r="O12" t="n">
-        <v>150.4</v>
+        <v>117.2</v>
       </c>
       <c r="P12" t="n">
-        <v>239</v>
+        <v>205.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="R12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
     </row>
     <row r="13">
@@ -1193,19 +1193,19 @@
         <v>9652</v>
       </c>
       <c r="N13" t="n">
-        <v>652.4</v>
+        <v>573.9</v>
       </c>
       <c r="O13" t="n">
-        <v>746.5</v>
+        <v>668</v>
       </c>
       <c r="P13" t="n">
-        <v>1250.9</v>
+        <v>1172.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>1870.1</v>
+        <v>1791.6</v>
       </c>
       <c r="R13" t="n">
-        <v>1870.1</v>
+        <v>1791.6</v>
       </c>
     </row>
     <row r="14">
@@ -1251,19 +1251,19 @@
         <v>135</v>
       </c>
       <c r="N14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O14" t="n">
-        <v>11.3</v>
+        <v>9.4</v>
       </c>
       <c r="P14" t="n">
-        <v>18.4</v>
+        <v>16.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="R14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="15">
@@ -1309,19 +1309,19 @@
         <v>9647</v>
       </c>
       <c r="N15" t="n">
-        <v>985</v>
+        <v>799.4</v>
       </c>
       <c r="O15" t="n">
-        <v>1079</v>
+        <v>893.4</v>
       </c>
       <c r="P15" t="n">
-        <v>1583.2</v>
+        <v>1397.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
       <c r="R15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
     </row>
     <row r="16">
@@ -1367,19 +1367,19 @@
         <v>7368</v>
       </c>
       <c r="N16" t="n">
-        <v>380.9</v>
+        <v>438.1</v>
       </c>
       <c r="O16" t="n">
-        <v>452.7</v>
+        <v>509.8</v>
       </c>
       <c r="P16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="R16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
     </row>
     <row r="17">
@@ -1425,19 +1425,19 @@
         <v>4056</v>
       </c>
       <c r="N17" t="n">
-        <v>320.7</v>
+        <v>241.2</v>
       </c>
       <c r="O17" t="n">
-        <v>360.3</v>
+        <v>280.7</v>
       </c>
       <c r="P17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="R17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
     </row>
     <row r="18">
@@ -1483,19 +1483,19 @@
         <v>192214</v>
       </c>
       <c r="N18" t="n">
-        <v>10070.7</v>
+        <v>11492.4</v>
       </c>
       <c r="O18" t="n">
-        <v>11953.4</v>
+        <v>13375.1</v>
       </c>
       <c r="P18" t="n">
-        <v>22054.2</v>
+        <v>23475.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="R18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
     </row>
     <row r="19">
@@ -1539,19 +1539,19 @@
         <v>69</v>
       </c>
       <c r="N19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="R19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="20">
@@ -1597,19 +1597,19 @@
         <v>475</v>
       </c>
       <c r="N20" t="n">
-        <v>24.6</v>
+        <v>28.3</v>
       </c>
       <c r="O20" t="n">
-        <v>29.2</v>
+        <v>32.9</v>
       </c>
       <c r="P20" t="n">
-        <v>54.1</v>
+        <v>57.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="R20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
     </row>
     <row r="21">
@@ -1655,19 +1655,19 @@
         <v>5265</v>
       </c>
       <c r="N21" t="n">
-        <v>416.4</v>
+        <v>313.1</v>
       </c>
       <c r="O21" t="n">
-        <v>467.7</v>
+        <v>364.4</v>
       </c>
       <c r="P21" t="n">
-        <v>742.9</v>
+        <v>639.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>2621.2</v>
+        <v>2517.8</v>
       </c>
       <c r="R21" t="n">
-        <v>2621.2</v>
+        <v>2517.8</v>
       </c>
     </row>
     <row r="22">
@@ -1713,19 +1713,19 @@
         <v>438</v>
       </c>
       <c r="N22" t="n">
-        <v>34.6</v>
+        <v>26</v>
       </c>
       <c r="O22" t="n">
-        <v>38.9</v>
+        <v>30.3</v>
       </c>
       <c r="P22" t="n">
-        <v>61.8</v>
+        <v>53.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="R22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
     </row>
     <row r="23">
@@ -1771,19 +1771,19 @@
         <v>4491</v>
       </c>
       <c r="N23" t="n">
-        <v>274.3</v>
+        <v>267</v>
       </c>
       <c r="O23" t="n">
-        <v>318</v>
+        <v>310.8</v>
       </c>
       <c r="P23" t="n">
-        <v>552.7</v>
+        <v>545.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>1365.2</v>
+        <v>1357.9</v>
       </c>
       <c r="R23" t="n">
-        <v>1365.2</v>
+        <v>1357.9</v>
       </c>
     </row>
     <row r="24">
@@ -1829,19 +1829,19 @@
         <v>6095</v>
       </c>
       <c r="N24" t="n">
-        <v>424</v>
+        <v>419.1</v>
       </c>
       <c r="O24" t="n">
-        <v>483.3</v>
+        <v>478.5</v>
       </c>
       <c r="P24" t="n">
-        <v>801.9</v>
+        <v>797</v>
       </c>
       <c r="Q24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
       <c r="R24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
     </row>
     <row r="25">
@@ -1887,19 +1887,19 @@
         <v>262</v>
       </c>
       <c r="N25" t="n">
-        <v>19.1</v>
+        <v>15.6</v>
       </c>
       <c r="O25" t="n">
-        <v>21.7</v>
+        <v>18.1</v>
       </c>
       <c r="P25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="R25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="26">
@@ -1945,19 +1945,19 @@
         <v>141</v>
       </c>
       <c r="N26" t="n">
-        <v>7.3</v>
+        <v>8.4</v>
       </c>
       <c r="O26" t="n">
-        <v>8.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>16</v>
+        <v>17.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
       <c r="R26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
     </row>
   </sheetData>
@@ -33320,235 +33320,235 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2222.4</v>
+        <v>2030</v>
       </c>
       <c r="C2" t="n">
-        <v>2271.1</v>
+        <v>2078.6</v>
       </c>
       <c r="D2" t="n">
-        <v>2328.1</v>
+        <v>2135.6</v>
       </c>
       <c r="E2" t="n">
-        <v>2385.9</v>
+        <v>2193.4</v>
       </c>
       <c r="F2" t="n">
-        <v>2444.7</v>
+        <v>2252.2</v>
       </c>
       <c r="G2" t="n">
-        <v>2504.4</v>
+        <v>2312</v>
       </c>
       <c r="H2" t="n">
-        <v>2555</v>
+        <v>2362.6</v>
       </c>
       <c r="I2" t="n">
-        <v>2616.4</v>
+        <v>2423.9</v>
       </c>
       <c r="J2" t="n">
-        <v>2678.9</v>
+        <v>2486.5</v>
       </c>
       <c r="K2" t="n">
-        <v>2710.9</v>
+        <v>2518.5</v>
       </c>
       <c r="L2" t="n">
-        <v>2808.2</v>
+        <v>2615.7</v>
       </c>
       <c r="M2" t="n">
-        <v>2862.8</v>
+        <v>2670.3</v>
       </c>
       <c r="N2" t="n">
-        <v>2931.7</v>
+        <v>2739.3</v>
       </c>
       <c r="O2" t="n">
-        <v>3003.5</v>
+        <v>2811</v>
       </c>
       <c r="P2" t="n">
-        <v>3077.7</v>
+        <v>2885.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>3155.1</v>
+        <v>2962.6</v>
       </c>
       <c r="R2" t="n">
-        <v>3219.5</v>
+        <v>3027.1</v>
       </c>
       <c r="S2" t="n">
-        <v>3277.3</v>
+        <v>3084.8</v>
       </c>
       <c r="T2" t="n">
-        <v>3337.7</v>
+        <v>3145.2</v>
       </c>
       <c r="U2" t="n">
-        <v>3399.9</v>
+        <v>3207.5</v>
       </c>
       <c r="V2" t="n">
-        <v>3464.2</v>
+        <v>3271.7</v>
       </c>
       <c r="W2" t="n">
-        <v>3530.6</v>
+        <v>3338.1</v>
       </c>
       <c r="X2" t="n">
-        <v>3599.3</v>
+        <v>3406.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>3670.4</v>
+        <v>3477.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>3744</v>
+        <v>3551.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>3820.2</v>
+        <v>3627.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>3899.3</v>
+        <v>3706.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>3981.1</v>
+        <v>3788.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>4066</v>
+        <v>3873.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>4153.9</v>
+        <v>3961.4</v>
       </c>
       <c r="AF2" t="n">
-        <v>4244.9</v>
+        <v>4052.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>4339.3</v>
+        <v>4146.8</v>
       </c>
       <c r="AH2" t="n">
-        <v>4437.1</v>
+        <v>4244.7</v>
       </c>
       <c r="AI2" t="n">
-        <v>4538.5</v>
+        <v>4346.1</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4642.8</v>
+        <v>4450.4</v>
       </c>
       <c r="AK2" t="n">
-        <v>4749.6</v>
+        <v>4557.2</v>
       </c>
       <c r="AL2" t="n">
-        <v>4859.2</v>
+        <v>4666.7</v>
       </c>
       <c r="AM2" t="n">
-        <v>4993.4</v>
+        <v>4800.9</v>
       </c>
       <c r="AN2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="AO2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="AP2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="AX2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="BA2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="BH2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="BI2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="BJ2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="BL2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="BM2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="BN2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="BO2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="BP2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="BR2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="BS2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="BT2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="BU2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="BV2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="BW2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="BX2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="BY2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
       <c r="BZ2" t="n">
-        <v>5108.9</v>
+        <v>4916.4</v>
       </c>
     </row>
     <row r="3">
@@ -33558,235 +33558,235 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>634.9</v>
+        <v>480.9</v>
       </c>
       <c r="C3" t="n">
-        <v>646.1</v>
+        <v>492.1</v>
       </c>
       <c r="D3" t="n">
-        <v>659.2</v>
+        <v>505.2</v>
       </c>
       <c r="E3" t="n">
-        <v>672.5</v>
+        <v>518.5</v>
       </c>
       <c r="F3" t="n">
-        <v>686</v>
+        <v>532</v>
       </c>
       <c r="G3" t="n">
-        <v>699.7</v>
+        <v>545.7</v>
       </c>
       <c r="H3" t="n">
-        <v>711.3</v>
+        <v>557.4</v>
       </c>
       <c r="I3" t="n">
-        <v>725.4</v>
+        <v>571.5</v>
       </c>
       <c r="J3" t="n">
-        <v>739.8</v>
+        <v>585.8</v>
       </c>
       <c r="K3" t="n">
-        <v>747.2</v>
+        <v>593.2</v>
       </c>
       <c r="L3" t="n">
-        <v>769.5</v>
+        <v>615.5</v>
       </c>
       <c r="M3" t="n">
-        <v>782.1</v>
+        <v>628.1</v>
       </c>
       <c r="N3" t="n">
-        <v>797.9</v>
+        <v>643.9</v>
       </c>
       <c r="O3" t="n">
-        <v>814.4</v>
+        <v>660.4</v>
       </c>
       <c r="P3" t="n">
-        <v>831.5</v>
+        <v>677.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>849.3</v>
+        <v>695.3</v>
       </c>
       <c r="R3" t="n">
-        <v>864.1</v>
+        <v>710.1</v>
       </c>
       <c r="S3" t="n">
-        <v>877.3</v>
+        <v>723.4</v>
       </c>
       <c r="T3" t="n">
-        <v>891.2</v>
+        <v>737.2</v>
       </c>
       <c r="U3" t="n">
-        <v>905.5</v>
+        <v>751.5</v>
       </c>
       <c r="V3" t="n">
-        <v>920.3</v>
+        <v>766.3</v>
       </c>
       <c r="W3" t="n">
-        <v>935.6</v>
+        <v>781.6</v>
       </c>
       <c r="X3" t="n">
-        <v>951.3</v>
+        <v>797.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>967.7</v>
+        <v>813.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>984.6</v>
+        <v>830.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>1002.1</v>
+        <v>848.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>1020.3</v>
+        <v>866.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>1039.1</v>
+        <v>885.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>1058.6</v>
+        <v>904.6</v>
       </c>
       <c r="AE3" t="n">
-        <v>1078.8</v>
+        <v>924.8</v>
       </c>
       <c r="AF3" t="n">
-        <v>1099.7</v>
+        <v>945.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>1121.4</v>
+        <v>967.4</v>
       </c>
       <c r="AH3" t="n">
-        <v>1143.9</v>
+        <v>989.9</v>
       </c>
       <c r="AI3" t="n">
-        <v>1167.2</v>
+        <v>1013.2</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1191.2</v>
+        <v>1037.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>1215.7</v>
+        <v>1061.8</v>
       </c>
       <c r="AL3" t="n">
-        <v>1240.9</v>
+        <v>1086.9</v>
       </c>
       <c r="AM3" t="n">
-        <v>1266.6</v>
+        <v>1112.6</v>
       </c>
       <c r="AN3" t="n">
-        <v>1392.8</v>
+        <v>1238.8</v>
       </c>
       <c r="AO3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="BI3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="BL3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="BM3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="BP3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="BR3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="BS3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="BT3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="BV3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="BW3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="BX3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="BY3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1991.5</v>
+        <v>1837.5</v>
       </c>
     </row>
     <row r="4">
@@ -33796,235 +33796,235 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>109.3</v>
+        <v>82.2</v>
       </c>
       <c r="C4" t="n">
-        <v>111.3</v>
+        <v>84.2</v>
       </c>
       <c r="D4" t="n">
-        <v>113.6</v>
+        <v>86.5</v>
       </c>
       <c r="E4" t="n">
-        <v>116</v>
+        <v>88.8</v>
       </c>
       <c r="F4" t="n">
-        <v>118.3</v>
+        <v>91.2</v>
       </c>
       <c r="G4" t="n">
-        <v>120.8</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>122.8</v>
+        <v>95.7</v>
       </c>
       <c r="I4" t="n">
-        <v>125.3</v>
+        <v>98.2</v>
       </c>
       <c r="J4" t="n">
-        <v>127.8</v>
+        <v>100.7</v>
       </c>
       <c r="K4" t="n">
-        <v>129.1</v>
+        <v>102</v>
       </c>
       <c r="L4" t="n">
-        <v>133.1</v>
+        <v>105.9</v>
       </c>
       <c r="M4" t="n">
-        <v>135.3</v>
+        <v>108.1</v>
       </c>
       <c r="N4" t="n">
-        <v>138.1</v>
+        <v>110.9</v>
       </c>
       <c r="O4" t="n">
-        <v>141</v>
+        <v>113.8</v>
       </c>
       <c r="P4" t="n">
-        <v>144</v>
+        <v>116.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="R4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="S4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="T4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="U4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="V4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="W4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="X4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="AG4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="AH4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="AI4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="AJ4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="AK4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="AL4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="AM4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="AN4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="AO4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="AP4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="BH4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="BJ4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="BK4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="BL4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="BM4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="BN4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="BP4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="BQ4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="BR4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="BS4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="BT4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="BU4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="BV4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="BW4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="BX4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="BY4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
       <c r="BZ4" t="n">
-        <v>144.3</v>
+        <v>117.2</v>
       </c>
     </row>
     <row r="5">
@@ -34034,235 +34034,235 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2247</v>
+        <v>1832.3</v>
       </c>
       <c r="C5" t="n">
-        <v>2291</v>
+        <v>1876.2</v>
       </c>
       <c r="D5" t="n">
-        <v>2342.4</v>
+        <v>1927.7</v>
       </c>
       <c r="E5" t="n">
-        <v>2394.6</v>
+        <v>1979.8</v>
       </c>
       <c r="F5" t="n">
-        <v>2447.6</v>
+        <v>2032.9</v>
       </c>
       <c r="G5" t="n">
-        <v>2501.6</v>
+        <v>2086.8</v>
       </c>
       <c r="H5" t="n">
-        <v>2547.2</v>
+        <v>2132.5</v>
       </c>
       <c r="I5" t="n">
-        <v>2602.6</v>
+        <v>2187.9</v>
       </c>
       <c r="J5" t="n">
-        <v>2659.1</v>
+        <v>2244.3</v>
       </c>
       <c r="K5" t="n">
-        <v>2688</v>
+        <v>2273.2</v>
       </c>
       <c r="L5" t="n">
-        <v>2775.8</v>
+        <v>2361</v>
       </c>
       <c r="M5" t="n">
-        <v>2825</v>
+        <v>2410.3</v>
       </c>
       <c r="N5" t="n">
-        <v>2887.3</v>
+        <v>2472.5</v>
       </c>
       <c r="O5" t="n">
-        <v>2952</v>
+        <v>2537.3</v>
       </c>
       <c r="P5" t="n">
-        <v>3019</v>
+        <v>2604.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>3088.9</v>
+        <v>2674.1</v>
       </c>
       <c r="R5" t="n">
-        <v>3147.1</v>
+        <v>2732.3</v>
       </c>
       <c r="S5" t="n">
-        <v>3199.2</v>
+        <v>2784.4</v>
       </c>
       <c r="T5" t="n">
-        <v>3253.7</v>
+        <v>2838.9</v>
       </c>
       <c r="U5" t="n">
-        <v>3309.9</v>
+        <v>2895.1</v>
       </c>
       <c r="V5" t="n">
-        <v>3367.9</v>
+        <v>2953.2</v>
       </c>
       <c r="W5" t="n">
-        <v>3427.8</v>
+        <v>3013.1</v>
       </c>
       <c r="X5" t="n">
-        <v>3489.8</v>
+        <v>3075.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>3554</v>
+        <v>3139.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>3620.4</v>
+        <v>3205.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>3689.3</v>
+        <v>3274.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>3760.6</v>
+        <v>3345.9</v>
       </c>
       <c r="AC5" t="n">
-        <v>3834.5</v>
+        <v>3419.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>3911.1</v>
+        <v>3496.3</v>
       </c>
       <c r="AE5" t="n">
-        <v>3990.4</v>
+        <v>3575.7</v>
       </c>
       <c r="AF5" t="n">
-        <v>4072.6</v>
+        <v>3657.9</v>
       </c>
       <c r="AG5" t="n">
-        <v>4157.8</v>
+        <v>3743</v>
       </c>
       <c r="AH5" t="n">
-        <v>4246.1</v>
+        <v>3831.3</v>
       </c>
       <c r="AI5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="AK5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="AL5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="AM5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="AN5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="AO5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="AP5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="AR5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="AS5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="AT5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="AU5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="AV5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="AW5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="AX5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="AY5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="BA5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="BB5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="BC5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="BD5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="BE5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="BF5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="BG5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="BH5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="BI5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="BJ5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="BK5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="BL5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="BM5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="BN5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="BO5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="BP5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="BR5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="BS5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="BT5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="BU5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="BV5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="BW5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="BX5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="BY5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
       <c r="BZ5" t="n">
-        <v>4273.5</v>
+        <v>3858.7</v>
       </c>
     </row>
     <row r="6">
@@ -34272,235 +34272,235 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>810.1</v>
+        <v>779.8</v>
       </c>
       <c r="C6" t="n">
-        <v>828.8</v>
+        <v>798.5</v>
       </c>
       <c r="D6" t="n">
-        <v>850.6</v>
+        <v>820.4</v>
       </c>
       <c r="E6" t="n">
-        <v>872.9</v>
+        <v>842.6</v>
       </c>
       <c r="F6" t="n">
-        <v>895.4</v>
+        <v>865.2</v>
       </c>
       <c r="G6" t="n">
-        <v>918.4</v>
+        <v>888.2</v>
       </c>
       <c r="H6" t="n">
-        <v>937.8</v>
+        <v>907.6</v>
       </c>
       <c r="I6" t="n">
-        <v>961.4</v>
+        <v>931.2</v>
       </c>
       <c r="J6" t="n">
-        <v>985.4</v>
+        <v>955.2</v>
       </c>
       <c r="K6" t="n">
-        <v>997.7</v>
+        <v>967.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1035.1</v>
+        <v>1004.8</v>
       </c>
       <c r="M6" t="n">
-        <v>1056</v>
+        <v>1025.8</v>
       </c>
       <c r="N6" t="n">
-        <v>1082.5</v>
+        <v>1052.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1110.1</v>
+        <v>1079.9</v>
       </c>
       <c r="P6" t="n">
-        <v>1138.6</v>
+        <v>1108.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>1168.3</v>
+        <v>1138.1</v>
       </c>
       <c r="R6" t="n">
-        <v>1193.1</v>
+        <v>1162.9</v>
       </c>
       <c r="S6" t="n">
-        <v>1215.3</v>
+        <v>1185</v>
       </c>
       <c r="T6" t="n">
-        <v>1238.5</v>
+        <v>1208.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1262.4</v>
+        <v>1232.2</v>
       </c>
       <c r="V6" t="n">
-        <v>1287.1</v>
+        <v>1256.8</v>
       </c>
       <c r="W6" t="n">
-        <v>1312.6</v>
+        <v>1282.4</v>
       </c>
       <c r="X6" t="n">
-        <v>1339</v>
+        <v>1308.7</v>
       </c>
       <c r="Y6" t="n">
-        <v>1366.3</v>
+        <v>1336</v>
       </c>
       <c r="Z6" t="n">
-        <v>1394.6</v>
+        <v>1364.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>1423.9</v>
+        <v>1393.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>1454.2</v>
+        <v>1424</v>
       </c>
       <c r="AC6" t="n">
-        <v>1485.7</v>
+        <v>1455.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1518.3</v>
+        <v>1488</v>
       </c>
       <c r="AE6" t="n">
-        <v>1552</v>
+        <v>1521.8</v>
       </c>
       <c r="AF6" t="n">
-        <v>1587</v>
+        <v>1556.8</v>
       </c>
       <c r="AG6" t="n">
-        <v>1623.3</v>
+        <v>1593</v>
       </c>
       <c r="AH6" t="n">
-        <v>1660.8</v>
+        <v>1630.6</v>
       </c>
       <c r="AI6" t="n">
-        <v>1791.3</v>
+        <v>1761.1</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1925.5</v>
+        <v>1895.3</v>
       </c>
       <c r="AK6" t="n">
-        <v>2063</v>
+        <v>2032.7</v>
       </c>
       <c r="AL6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="AM6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="AN6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="AO6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="AP6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="AX6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="AY6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="BA6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="BH6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="BI6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="BJ6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="BK6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="BL6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="BM6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="BN6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="BO6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="BP6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="BQ6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="BR6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="BS6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="BT6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="BU6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="BV6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="BW6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="BX6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="BY6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2087.7</v>
+        <v>2057.4</v>
       </c>
     </row>
     <row r="7">
@@ -34510,235 +34510,235 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>146.7</v>
+        <v>110.3</v>
       </c>
       <c r="C7" t="n">
-        <v>149.3</v>
+        <v>112.9</v>
       </c>
       <c r="D7" t="n">
-        <v>152.4</v>
+        <v>116</v>
       </c>
       <c r="E7" t="n">
-        <v>155.6</v>
+        <v>119.2</v>
       </c>
       <c r="F7" t="n">
-        <v>158.8</v>
+        <v>122.4</v>
       </c>
       <c r="G7" t="n">
-        <v>162</v>
+        <v>125.6</v>
       </c>
       <c r="H7" t="n">
-        <v>164.8</v>
+        <v>128.4</v>
       </c>
       <c r="I7" t="n">
-        <v>168.1</v>
+        <v>131.7</v>
       </c>
       <c r="J7" t="n">
-        <v>171.5</v>
+        <v>135.1</v>
       </c>
       <c r="K7" t="n">
-        <v>173.2</v>
+        <v>136.8</v>
       </c>
       <c r="L7" t="n">
-        <v>178.5</v>
+        <v>142.1</v>
       </c>
       <c r="M7" t="n">
-        <v>181.5</v>
+        <v>145.1</v>
       </c>
       <c r="N7" t="n">
-        <v>185.2</v>
+        <v>148.8</v>
       </c>
       <c r="O7" t="n">
-        <v>189.1</v>
+        <v>152.7</v>
       </c>
       <c r="P7" t="n">
-        <v>193.2</v>
+        <v>156.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>197.4</v>
+        <v>161</v>
       </c>
       <c r="R7" t="n">
-        <v>200.9</v>
+        <v>164.5</v>
       </c>
       <c r="S7" t="n">
-        <v>204</v>
+        <v>167.6</v>
       </c>
       <c r="T7" t="n">
-        <v>207.3</v>
+        <v>170.9</v>
       </c>
       <c r="U7" t="n">
-        <v>210.7</v>
+        <v>174.3</v>
       </c>
       <c r="V7" t="n">
-        <v>214.2</v>
+        <v>177.8</v>
       </c>
       <c r="W7" t="n">
-        <v>217.8</v>
+        <v>181.4</v>
       </c>
       <c r="X7" t="n">
-        <v>221.5</v>
+        <v>185.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>225.4</v>
+        <v>189</v>
       </c>
       <c r="Z7" t="n">
-        <v>229.4</v>
+        <v>193</v>
       </c>
       <c r="AA7" t="n">
-        <v>233.5</v>
+        <v>197.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>237.8</v>
+        <v>201.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>242.3</v>
+        <v>205.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>263.3</v>
+        <v>226.9</v>
       </c>
       <c r="AE7" t="n">
-        <v>287.1</v>
+        <v>250.7</v>
       </c>
       <c r="AF7" t="n">
-        <v>311.7</v>
+        <v>275.3</v>
       </c>
       <c r="AG7" t="n">
-        <v>337.2</v>
+        <v>300.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>363.6</v>
+        <v>327.2</v>
       </c>
       <c r="AI7" t="n">
-        <v>391</v>
+        <v>354.6</v>
       </c>
       <c r="AJ7" t="n">
-        <v>419.2</v>
+        <v>382.8</v>
       </c>
       <c r="AK7" t="n">
-        <v>448</v>
+        <v>411.6</v>
       </c>
       <c r="AL7" t="n">
-        <v>477.6</v>
+        <v>441.2</v>
       </c>
       <c r="AM7" t="n">
-        <v>507.8</v>
+        <v>471.4</v>
       </c>
       <c r="AN7" t="n">
-        <v>538.8</v>
+        <v>502.4</v>
       </c>
       <c r="AO7" t="n">
-        <v>570.5</v>
+        <v>534.1</v>
       </c>
       <c r="AP7" t="n">
-        <v>603</v>
+        <v>566.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>636.3</v>
+        <v>599.9</v>
       </c>
       <c r="AR7" t="n">
-        <v>670.4</v>
+        <v>634</v>
       </c>
       <c r="AS7" t="n">
-        <v>705.2</v>
+        <v>668.8</v>
       </c>
       <c r="AT7" t="n">
-        <v>741</v>
+        <v>704.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>777.5</v>
+        <v>741.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>815</v>
+        <v>778.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>852.4</v>
+        <v>816</v>
       </c>
       <c r="AX7" t="n">
-        <v>852.4</v>
+        <v>816</v>
       </c>
       <c r="AY7" t="n">
-        <v>852.4</v>
+        <v>816</v>
       </c>
       <c r="AZ7" t="n">
-        <v>852.4</v>
+        <v>816</v>
       </c>
       <c r="BA7" t="n">
-        <v>852.4</v>
+        <v>816</v>
       </c>
       <c r="BB7" t="n">
-        <v>852.4</v>
+        <v>816</v>
       </c>
       <c r="BC7" t="n">
-        <v>852.4</v>
+        <v>816</v>
       </c>
       <c r="BD7" t="n">
-        <v>852.4</v>
+        <v>816</v>
       </c>
       <c r="BE7" t="n">
-        <v>852.4</v>
+        <v>816</v>
       </c>
       <c r="BF7" t="n">
-        <v>852.4</v>
+        <v>816</v>
       </c>
       <c r="BG7" t="n">
-        <v>852.4</v>
+        <v>816</v>
       </c>
       <c r="BH7" t="n">
-        <v>852.4</v>
+        <v>816</v>
       </c>
       <c r="BI7" t="n">
-        <v>852.4</v>
+        <v>816</v>
       </c>
       <c r="BJ7" t="n">
-        <v>852.4</v>
+        <v>816</v>
       </c>
       <c r="BK7" t="n">
-        <v>852.4</v>
+        <v>816</v>
       </c>
       <c r="BL7" t="n">
-        <v>852.4</v>
+        <v>816</v>
       </c>
       <c r="BM7" t="n">
-        <v>852.4</v>
+        <v>816</v>
       </c>
       <c r="BN7" t="n">
-        <v>852.4</v>
+        <v>816</v>
       </c>
       <c r="BO7" t="n">
-        <v>852.4</v>
+        <v>816</v>
       </c>
       <c r="BP7" t="n">
-        <v>852.4</v>
+        <v>816</v>
       </c>
       <c r="BQ7" t="n">
-        <v>852.4</v>
+        <v>816</v>
       </c>
       <c r="BR7" t="n">
-        <v>852.4</v>
+        <v>816</v>
       </c>
       <c r="BS7" t="n">
-        <v>852.4</v>
+        <v>816</v>
       </c>
       <c r="BT7" t="n">
-        <v>852.4</v>
+        <v>816</v>
       </c>
       <c r="BU7" t="n">
-        <v>852.4</v>
+        <v>816</v>
       </c>
       <c r="BV7" t="n">
-        <v>852.4</v>
+        <v>816</v>
       </c>
       <c r="BW7" t="n">
-        <v>852.4</v>
+        <v>816</v>
       </c>
       <c r="BX7" t="n">
-        <v>852.4</v>
+        <v>816</v>
       </c>
       <c r="BY7" t="n">
-        <v>852.4</v>
+        <v>816</v>
       </c>
       <c r="BZ7" t="n">
-        <v>852.4</v>
+        <v>816</v>
       </c>
     </row>
     <row r="8">
@@ -34748,235 +34748,235 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>313.5</v>
+        <v>235.7</v>
       </c>
       <c r="C8" t="n">
-        <v>319.1</v>
+        <v>241.3</v>
       </c>
       <c r="D8" t="n">
-        <v>325.7</v>
+        <v>247.9</v>
       </c>
       <c r="E8" t="n">
-        <v>332.4</v>
+        <v>254.7</v>
       </c>
       <c r="F8" t="n">
-        <v>339.3</v>
+        <v>261.5</v>
       </c>
       <c r="G8" t="n">
-        <v>346.2</v>
+        <v>268.4</v>
       </c>
       <c r="H8" t="n">
-        <v>352.1</v>
+        <v>274.3</v>
       </c>
       <c r="I8" t="n">
-        <v>359.2</v>
+        <v>281.4</v>
       </c>
       <c r="J8" t="n">
-        <v>366.5</v>
+        <v>288.7</v>
       </c>
       <c r="K8" t="n">
-        <v>370.2</v>
+        <v>292.4</v>
       </c>
       <c r="L8" t="n">
-        <v>381.5</v>
+        <v>303.7</v>
       </c>
       <c r="M8" t="n">
-        <v>387.8</v>
+        <v>310</v>
       </c>
       <c r="N8" t="n">
-        <v>395.8</v>
+        <v>318</v>
       </c>
       <c r="O8" t="n">
-        <v>404.1</v>
+        <v>326.4</v>
       </c>
       <c r="P8" t="n">
-        <v>412.7</v>
+        <v>335</v>
       </c>
       <c r="Q8" t="n">
-        <v>421.7</v>
+        <v>344</v>
       </c>
       <c r="R8" t="n">
-        <v>429.2</v>
+        <v>351.4</v>
       </c>
       <c r="S8" t="n">
-        <v>435.9</v>
+        <v>358.1</v>
       </c>
       <c r="T8" t="n">
-        <v>442.9</v>
+        <v>365.2</v>
       </c>
       <c r="U8" t="n">
-        <v>450.2</v>
+        <v>372.4</v>
       </c>
       <c r="V8" t="n">
-        <v>457.6</v>
+        <v>379.9</v>
       </c>
       <c r="W8" t="n">
-        <v>465.3</v>
+        <v>387.6</v>
       </c>
       <c r="X8" t="n">
-        <v>473.3</v>
+        <v>395.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>481.6</v>
+        <v>403.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>490.1</v>
+        <v>412.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>499</v>
+        <v>421.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>508.1</v>
+        <v>430.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>517.6</v>
+        <v>439.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>527.5</v>
+        <v>449.7</v>
       </c>
       <c r="AE8" t="n">
-        <v>537.7</v>
+        <v>459.9</v>
       </c>
       <c r="AF8" t="n">
-        <v>548.3</v>
+        <v>470.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>559.2</v>
+        <v>481.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>570.6</v>
+        <v>492.8</v>
       </c>
       <c r="AI8" t="n">
-        <v>582.3</v>
+        <v>504.6</v>
       </c>
       <c r="AJ8" t="n">
-        <v>594.5</v>
+        <v>516.7</v>
       </c>
       <c r="AK8" t="n">
-        <v>606.9</v>
+        <v>529.1</v>
       </c>
       <c r="AL8" t="n">
-        <v>619.6</v>
+        <v>541.8</v>
       </c>
       <c r="AM8" t="n">
-        <v>638.9</v>
+        <v>561.1</v>
       </c>
       <c r="AN8" t="n">
-        <v>673.5</v>
+        <v>595.7</v>
       </c>
       <c r="AO8" t="n">
-        <v>775.1</v>
+        <v>697.3</v>
       </c>
       <c r="AP8" t="n">
-        <v>1492.2</v>
+        <v>1414.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="BH8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="BI8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="BL8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="BM8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="BP8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="BR8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="BS8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="BT8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="BV8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="BX8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="BY8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1493.2</v>
+        <v>1415.5</v>
       </c>
     </row>
     <row r="9">
@@ -34986,235 +34986,235 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>477.5</v>
+        <v>459.7</v>
       </c>
       <c r="C9" t="n">
-        <v>488.6</v>
+        <v>470.9</v>
       </c>
       <c r="D9" t="n">
-        <v>501.6</v>
+        <v>483.9</v>
       </c>
       <c r="E9" t="n">
-        <v>514.8</v>
+        <v>497.1</v>
       </c>
       <c r="F9" t="n">
-        <v>528.3</v>
+        <v>510.5</v>
       </c>
       <c r="G9" t="n">
-        <v>541.9</v>
+        <v>524.2</v>
       </c>
       <c r="H9" t="n">
-        <v>553.5</v>
+        <v>535.7</v>
       </c>
       <c r="I9" t="n">
-        <v>567.5</v>
+        <v>549.7</v>
       </c>
       <c r="J9" t="n">
-        <v>581.8</v>
+        <v>564</v>
       </c>
       <c r="K9" t="n">
-        <v>589.1</v>
+        <v>571.4</v>
       </c>
       <c r="L9" t="n">
-        <v>611.3</v>
+        <v>593.6</v>
       </c>
       <c r="M9" t="n">
-        <v>623.8</v>
+        <v>606</v>
       </c>
       <c r="N9" t="n">
-        <v>639.5</v>
+        <v>621.8</v>
       </c>
       <c r="O9" t="n">
-        <v>655.9</v>
+        <v>638.2</v>
       </c>
       <c r="P9" t="n">
-        <v>672.9</v>
+        <v>655.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>690.6</v>
+        <v>672.8</v>
       </c>
       <c r="R9" t="n">
-        <v>705.3</v>
+        <v>687.6</v>
       </c>
       <c r="S9" t="n">
-        <v>718.5</v>
+        <v>700.8</v>
       </c>
       <c r="T9" t="n">
-        <v>732.3</v>
+        <v>714.6</v>
       </c>
       <c r="U9" t="n">
-        <v>746.5</v>
+        <v>728.8</v>
       </c>
       <c r="V9" t="n">
-        <v>761.2</v>
+        <v>743.5</v>
       </c>
       <c r="W9" t="n">
-        <v>776.4</v>
+        <v>758.6</v>
       </c>
       <c r="X9" t="n">
-        <v>792.1</v>
+        <v>774.3</v>
       </c>
       <c r="Y9" t="n">
-        <v>808.3</v>
+        <v>790.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>825.1</v>
+        <v>807.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>842.5</v>
+        <v>824.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>860.6</v>
+        <v>842.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>879.3</v>
+        <v>861.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>898.7</v>
+        <v>881</v>
       </c>
       <c r="AE9" t="n">
-        <v>918.8</v>
+        <v>901</v>
       </c>
       <c r="AF9" t="n">
-        <v>939.6</v>
+        <v>921.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>961.1</v>
+        <v>943.4</v>
       </c>
       <c r="AH9" t="n">
-        <v>983.5</v>
+        <v>965.8</v>
       </c>
       <c r="AI9" t="n">
-        <v>1006.7</v>
+        <v>988.9</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1030.5</v>
+        <v>1012.8</v>
       </c>
       <c r="AK9" t="n">
-        <v>1054.9</v>
+        <v>1037.2</v>
       </c>
       <c r="AL9" t="n">
-        <v>1079.9</v>
+        <v>1062.2</v>
       </c>
       <c r="AM9" t="n">
-        <v>1105.5</v>
+        <v>1087.7</v>
       </c>
       <c r="AN9" t="n">
-        <v>1131.7</v>
+        <v>1113.9</v>
       </c>
       <c r="AO9" t="n">
-        <v>1158.5</v>
+        <v>1140.8</v>
       </c>
       <c r="AP9" t="n">
-        <v>1186</v>
+        <v>1168.3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1214.1</v>
+        <v>1196.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>1242.9</v>
+        <v>1225.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>1272.4</v>
+        <v>1254.7</v>
       </c>
       <c r="AT9" t="n">
-        <v>1302.7</v>
+        <v>1284.9</v>
       </c>
       <c r="AU9" t="n">
-        <v>1342</v>
+        <v>1324.3</v>
       </c>
       <c r="AV9" t="n">
-        <v>1506.9</v>
+        <v>1489.2</v>
       </c>
       <c r="AW9" t="n">
-        <v>1806.3</v>
+        <v>1788.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>2414</v>
+        <v>2396.2</v>
       </c>
       <c r="AY9" t="n">
-        <v>2414</v>
+        <v>2396.2</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2414</v>
+        <v>2396.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>2414</v>
+        <v>2396.2</v>
       </c>
       <c r="BB9" t="n">
-        <v>2414</v>
+        <v>2396.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>2414</v>
+        <v>2396.2</v>
       </c>
       <c r="BD9" t="n">
-        <v>2414</v>
+        <v>2396.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>2414</v>
+        <v>2396.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>2414</v>
+        <v>2396.2</v>
       </c>
       <c r="BG9" t="n">
-        <v>2414</v>
+        <v>2396.2</v>
       </c>
       <c r="BH9" t="n">
-        <v>2414</v>
+        <v>2396.2</v>
       </c>
       <c r="BI9" t="n">
-        <v>2414</v>
+        <v>2396.2</v>
       </c>
       <c r="BJ9" t="n">
-        <v>2414</v>
+        <v>2396.2</v>
       </c>
       <c r="BK9" t="n">
-        <v>2414</v>
+        <v>2396.2</v>
       </c>
       <c r="BL9" t="n">
-        <v>2414</v>
+        <v>2396.2</v>
       </c>
       <c r="BM9" t="n">
-        <v>2414</v>
+        <v>2396.2</v>
       </c>
       <c r="BN9" t="n">
-        <v>2414</v>
+        <v>2396.2</v>
       </c>
       <c r="BO9" t="n">
-        <v>2414</v>
+        <v>2396.2</v>
       </c>
       <c r="BP9" t="n">
-        <v>2414</v>
+        <v>2396.2</v>
       </c>
       <c r="BQ9" t="n">
-        <v>2414</v>
+        <v>2396.2</v>
       </c>
       <c r="BR9" t="n">
-        <v>2414</v>
+        <v>2396.2</v>
       </c>
       <c r="BS9" t="n">
-        <v>2414</v>
+        <v>2396.2</v>
       </c>
       <c r="BT9" t="n">
-        <v>2414</v>
+        <v>2396.2</v>
       </c>
       <c r="BU9" t="n">
-        <v>2414</v>
+        <v>2396.2</v>
       </c>
       <c r="BV9" t="n">
-        <v>2414</v>
+        <v>2396.2</v>
       </c>
       <c r="BW9" t="n">
-        <v>2414</v>
+        <v>2396.2</v>
       </c>
       <c r="BX9" t="n">
-        <v>2414</v>
+        <v>2396.2</v>
       </c>
       <c r="BY9" t="n">
-        <v>2414</v>
+        <v>2396.2</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2414</v>
+        <v>2396.2</v>
       </c>
     </row>
     <row r="10">
@@ -35224,235 +35224,235 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>102.2</v>
+        <v>81.7</v>
       </c>
       <c r="C10" t="n">
-        <v>103.7</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>105.5</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>107.2</v>
+        <v>86.7</v>
       </c>
       <c r="F10" t="n">
-        <v>109</v>
+        <v>88.5</v>
       </c>
       <c r="G10" t="n">
-        <v>110.9</v>
+        <v>90.3</v>
       </c>
       <c r="H10" t="n">
-        <v>112.4</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>114.3</v>
+        <v>93.7</v>
       </c>
       <c r="J10" t="n">
-        <v>116.2</v>
+        <v>95.7</v>
       </c>
       <c r="K10" t="n">
-        <v>117.2</v>
+        <v>96.7</v>
       </c>
       <c r="L10" t="n">
-        <v>120.2</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>121.9</v>
+        <v>101.3</v>
       </c>
       <c r="N10" t="n">
-        <v>124</v>
+        <v>103.4</v>
       </c>
       <c r="O10" t="n">
-        <v>126.2</v>
+        <v>105.6</v>
       </c>
       <c r="P10" t="n">
-        <v>128.5</v>
+        <v>107.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>130.9</v>
+        <v>110.3</v>
       </c>
       <c r="R10" t="n">
-        <v>132.8</v>
+        <v>112.3</v>
       </c>
       <c r="S10" t="n">
-        <v>134.6</v>
+        <v>114</v>
       </c>
       <c r="T10" t="n">
-        <v>136.5</v>
+        <v>115.9</v>
       </c>
       <c r="U10" t="n">
-        <v>138.4</v>
+        <v>117.8</v>
       </c>
       <c r="V10" t="n">
-        <v>140.4</v>
+        <v>119.8</v>
       </c>
       <c r="W10" t="n">
-        <v>142.4</v>
+        <v>121.8</v>
       </c>
       <c r="X10" t="n">
-        <v>144.5</v>
+        <v>123.9</v>
       </c>
       <c r="Y10" t="n">
+        <v>126.1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>128.4</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>130.7</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>133.1</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>135.7</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>138.3</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>141</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>143.8</v>
+      </c>
+      <c r="AG10" t="n">
         <v>146.7</v>
       </c>
-      <c r="Z10" t="n">
-        <v>148.9</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>151.3</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>153.7</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>156.2</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>158.8</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>161.5</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>164.3</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>167.2</v>
-      </c>
       <c r="AH10" t="n">
-        <v>170.2</v>
+        <v>149.7</v>
       </c>
       <c r="AI10" t="n">
-        <v>173.3</v>
+        <v>152.8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>176.6</v>
+        <v>156</v>
       </c>
       <c r="AK10" t="n">
-        <v>179.8</v>
+        <v>159.3</v>
       </c>
       <c r="AL10" t="n">
-        <v>183.2</v>
+        <v>162.6</v>
       </c>
       <c r="AM10" t="n">
-        <v>186.6</v>
+        <v>166.1</v>
       </c>
       <c r="AN10" t="n">
-        <v>190.2</v>
+        <v>169.6</v>
       </c>
       <c r="AO10" t="n">
-        <v>193.8</v>
+        <v>173.2</v>
       </c>
       <c r="AP10" t="n">
-        <v>197.5</v>
+        <v>176.9</v>
       </c>
       <c r="AQ10" t="n">
-        <v>235.1</v>
+        <v>214.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>273.7</v>
+        <v>253.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>313.3</v>
+        <v>292.7</v>
       </c>
       <c r="AT10" t="n">
-        <v>353.7</v>
+        <v>333.2</v>
       </c>
       <c r="AU10" t="n">
-        <v>395.2</v>
+        <v>374.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
       <c r="AW10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
       <c r="AX10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
       <c r="AY10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
       <c r="AZ10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
       <c r="BA10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
       <c r="BB10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
       <c r="BC10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
       <c r="BD10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
       <c r="BE10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
       <c r="BF10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
       <c r="BG10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
       <c r="BH10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
       <c r="BI10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
       <c r="BJ10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
       <c r="BK10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
       <c r="BL10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
       <c r="BM10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
       <c r="BN10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
       <c r="BO10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
       <c r="BP10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
       <c r="BQ10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
       <c r="BR10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
       <c r="BS10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
       <c r="BT10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
       <c r="BU10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
       <c r="BV10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
       <c r="BW10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
       <c r="BX10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
       <c r="BY10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
       <c r="BZ10" t="n">
-        <v>945.6</v>
+        <v>925</v>
       </c>
     </row>
     <row r="11">
@@ -35462,235 +35462,235 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>38.4</v>
       </c>
       <c r="C11" t="n">
-        <v>51.9</v>
+        <v>39.3</v>
       </c>
       <c r="D11" t="n">
-        <v>53</v>
+        <v>40.4</v>
       </c>
       <c r="E11" t="n">
-        <v>54.1</v>
+        <v>41.5</v>
       </c>
       <c r="F11" t="n">
-        <v>55.2</v>
+        <v>42.6</v>
       </c>
       <c r="G11" t="n">
-        <v>56.4</v>
+        <v>43.7</v>
       </c>
       <c r="H11" t="n">
-        <v>57.3</v>
+        <v>44.7</v>
       </c>
       <c r="I11" t="n">
-        <v>58.5</v>
+        <v>45.8</v>
       </c>
       <c r="J11" t="n">
-        <v>59.7</v>
+        <v>47</v>
       </c>
       <c r="K11" t="n">
-        <v>60.3</v>
+        <v>47.6</v>
       </c>
       <c r="L11" t="n">
-        <v>62.1</v>
+        <v>49.4</v>
       </c>
       <c r="M11" t="n">
-        <v>63.1</v>
+        <v>50.5</v>
       </c>
       <c r="N11" t="n">
-        <v>64.40000000000001</v>
+        <v>51.8</v>
       </c>
       <c r="O11" t="n">
-        <v>65.8</v>
+        <v>53.1</v>
       </c>
       <c r="P11" t="n">
-        <v>67.2</v>
+        <v>54.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>71.5</v>
+        <v>58.8</v>
       </c>
       <c r="R11" t="n">
-        <v>75.3</v>
+        <v>62.7</v>
       </c>
       <c r="S11" t="n">
-        <v>78.7</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>82.3</v>
+        <v>69.7</v>
       </c>
       <c r="U11" t="n">
-        <v>86</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>89.8</v>
+        <v>77.2</v>
       </c>
       <c r="W11" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="X11" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="Z11" t="n">
         <v>93.8</v>
       </c>
-      <c r="X11" t="n">
-        <v>97.90000000000001</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>102.1</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>106.5</v>
-      </c>
       <c r="AA11" t="n">
-        <v>111</v>
+        <v>98.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>115.7</v>
+        <v>103</v>
       </c>
       <c r="AC11" t="n">
-        <v>120.6</v>
+        <v>107.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>125.6</v>
+        <v>112.9</v>
       </c>
       <c r="AE11" t="n">
-        <v>130.8</v>
+        <v>118.2</v>
       </c>
       <c r="AF11" t="n">
-        <v>140.9</v>
+        <v>128.3</v>
       </c>
       <c r="AG11" t="n">
-        <v>158.5</v>
+        <v>145.8</v>
       </c>
       <c r="AH11" t="n">
-        <v>176.6</v>
+        <v>164</v>
       </c>
       <c r="AI11" t="n">
-        <v>195.5</v>
+        <v>182.8</v>
       </c>
       <c r="AJ11" t="n">
-        <v>214.9</v>
+        <v>202.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>234.7</v>
+        <v>222.1</v>
       </c>
       <c r="AL11" t="n">
-        <v>255.1</v>
+        <v>242.4</v>
       </c>
       <c r="AM11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="AN11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="AO11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="AP11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="AQ11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="AR11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="AS11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="AT11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="AU11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="AV11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="AW11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="AX11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="AY11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="AZ11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="BA11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="BB11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="BC11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="BD11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="BE11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="BF11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="BG11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="BH11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="BI11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="BJ11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="BK11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="BL11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="BM11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="BN11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="BO11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="BP11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="BQ11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="BR11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="BS11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="BT11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="BU11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="BV11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="BW11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="BX11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="BY11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
       <c r="BZ11" t="n">
-        <v>269.6</v>
+        <v>256.9</v>
       </c>
     </row>
     <row r="12">
@@ -35700,235 +35700,235 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>133.9</v>
+        <v>100.7</v>
       </c>
       <c r="C12" t="n">
-        <v>136.4</v>
+        <v>103.1</v>
       </c>
       <c r="D12" t="n">
-        <v>139.2</v>
+        <v>106</v>
       </c>
       <c r="E12" t="n">
-        <v>142.1</v>
+        <v>108.8</v>
       </c>
       <c r="F12" t="n">
-        <v>145</v>
+        <v>111.7</v>
       </c>
       <c r="G12" t="n">
-        <v>147.9</v>
+        <v>114.7</v>
       </c>
       <c r="H12" t="n">
-        <v>150.4</v>
+        <v>117.2</v>
       </c>
       <c r="I12" t="n">
-        <v>153.5</v>
+        <v>120.3</v>
       </c>
       <c r="J12" t="n">
-        <v>156.6</v>
+        <v>123.4</v>
       </c>
       <c r="K12" t="n">
-        <v>158.2</v>
+        <v>124.9</v>
       </c>
       <c r="L12" t="n">
-        <v>163</v>
+        <v>129.8</v>
       </c>
       <c r="M12" t="n">
-        <v>165.7</v>
+        <v>132.5</v>
       </c>
       <c r="N12" t="n">
-        <v>169.1</v>
+        <v>135.9</v>
       </c>
       <c r="O12" t="n">
-        <v>172.7</v>
+        <v>139.5</v>
       </c>
       <c r="P12" t="n">
-        <v>176.4</v>
+        <v>143.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>180.2</v>
+        <v>147</v>
       </c>
       <c r="R12" t="n">
-        <v>183.4</v>
+        <v>150.2</v>
       </c>
       <c r="S12" t="n">
-        <v>186.3</v>
+        <v>153</v>
       </c>
       <c r="T12" t="n">
-        <v>189.3</v>
+        <v>156</v>
       </c>
       <c r="U12" t="n">
-        <v>192.4</v>
+        <v>159.1</v>
       </c>
       <c r="V12" t="n">
-        <v>195.6</v>
+        <v>162.3</v>
       </c>
       <c r="W12" t="n">
-        <v>198.8</v>
+        <v>165.6</v>
       </c>
       <c r="X12" t="n">
-        <v>202.3</v>
+        <v>169</v>
       </c>
       <c r="Y12" t="n">
-        <v>205.8</v>
+        <v>172.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>209.4</v>
+        <v>176.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>213.2</v>
+        <v>180</v>
       </c>
       <c r="AB12" t="n">
-        <v>217.1</v>
+        <v>183.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>221.2</v>
+        <v>188</v>
       </c>
       <c r="AD12" t="n">
-        <v>225.4</v>
+        <v>192.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>229.8</v>
+        <v>196.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>234.3</v>
+        <v>201.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>239</v>
+        <v>205.7</v>
       </c>
       <c r="AH12" t="n">
-        <v>243.8</v>
+        <v>210.6</v>
       </c>
       <c r="AI12" t="n">
-        <v>541</v>
+        <v>507.8</v>
       </c>
       <c r="AJ12" t="n">
-        <v>870.9</v>
+        <v>837.7</v>
       </c>
       <c r="AK12" t="n">
-        <v>1208.8</v>
+        <v>1175.6</v>
       </c>
       <c r="AL12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="AM12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="AN12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="AO12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="AP12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="AR12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="AS12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="AT12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="AU12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="AV12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="AW12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="AX12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="AY12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="BA12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="BB12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="BC12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="BD12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="BE12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="BF12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="BG12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="BH12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="BI12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="BK12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="BL12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="BM12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="BN12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="BO12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="BP12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="BR12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="BS12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="BT12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="BU12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="BV12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="BW12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="BX12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="BY12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1467.9</v>
+        <v>1434.7</v>
       </c>
     </row>
     <row r="13">
@@ -35938,235 +35938,235 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>652.4</v>
+        <v>573.9</v>
       </c>
       <c r="C13" t="n">
-        <v>666.2</v>
+        <v>587.7</v>
       </c>
       <c r="D13" t="n">
-        <v>682.3</v>
+        <v>603.8</v>
       </c>
       <c r="E13" t="n">
-        <v>698.6</v>
+        <v>620.2</v>
       </c>
       <c r="F13" t="n">
-        <v>715.3</v>
+        <v>636.8</v>
       </c>
       <c r="G13" t="n">
-        <v>732.2</v>
+        <v>653.7</v>
       </c>
       <c r="H13" t="n">
-        <v>746.5</v>
+        <v>668</v>
       </c>
       <c r="I13" t="n">
-        <v>763.8</v>
+        <v>685.3</v>
       </c>
       <c r="J13" t="n">
-        <v>781.5</v>
+        <v>703</v>
       </c>
       <c r="K13" t="n">
-        <v>790.5</v>
+        <v>712.1</v>
       </c>
       <c r="L13" t="n">
-        <v>818</v>
+        <v>739.6</v>
       </c>
       <c r="M13" t="n">
-        <v>833.5</v>
+        <v>755</v>
       </c>
       <c r="N13" t="n">
-        <v>853</v>
+        <v>774.5</v>
       </c>
       <c r="O13" t="n">
-        <v>873.2</v>
+        <v>794.8</v>
       </c>
       <c r="P13" t="n">
-        <v>894.2</v>
+        <v>815.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>916.1</v>
+        <v>837.6</v>
       </c>
       <c r="R13" t="n">
-        <v>934.3</v>
+        <v>855.9</v>
       </c>
       <c r="S13" t="n">
-        <v>950.7</v>
+        <v>872.2</v>
       </c>
       <c r="T13" t="n">
-        <v>967.7</v>
+        <v>889.3</v>
       </c>
       <c r="U13" t="n">
-        <v>985.3</v>
+        <v>906.9</v>
       </c>
       <c r="V13" t="n">
-        <v>1003.5</v>
+        <v>925</v>
       </c>
       <c r="W13" t="n">
-        <v>1022.3</v>
+        <v>943.8</v>
       </c>
       <c r="X13" t="n">
-        <v>1041.7</v>
+        <v>963.2</v>
       </c>
       <c r="Y13" t="n">
-        <v>1061.8</v>
+        <v>983.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>1082.6</v>
+        <v>1004.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1104.2</v>
+        <v>1025.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>1126.5</v>
+        <v>1048</v>
       </c>
       <c r="AC13" t="n">
-        <v>1149.7</v>
+        <v>1071.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>1173.7</v>
+        <v>1095.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>1198.5</v>
+        <v>1120</v>
       </c>
       <c r="AF13" t="n">
-        <v>1224.3</v>
+        <v>1145.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>1250.9</v>
+        <v>1172.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>1278.6</v>
+        <v>1200.1</v>
       </c>
       <c r="AI13" t="n">
-        <v>1307.3</v>
+        <v>1228.8</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1336.8</v>
+        <v>1258.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>1367</v>
+        <v>1288.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>1397.9</v>
+        <v>1319.4</v>
       </c>
       <c r="AM13" t="n">
-        <v>1429.5</v>
+        <v>1351.1</v>
       </c>
       <c r="AN13" t="n">
-        <v>1462.4</v>
+        <v>1383.9</v>
       </c>
       <c r="AO13" t="n">
-        <v>1496.1</v>
+        <v>1417.6</v>
       </c>
       <c r="AP13" t="n">
-        <v>1530.6</v>
+        <v>1452.1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1565.9</v>
+        <v>1487.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>1602</v>
+        <v>1523.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>1639.1</v>
+        <v>1560.6</v>
       </c>
       <c r="AT13" t="n">
-        <v>1677</v>
+        <v>1598.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>1715.8</v>
+        <v>1637.3</v>
       </c>
       <c r="AV13" t="n">
-        <v>1757.5</v>
+        <v>1679</v>
       </c>
       <c r="AW13" t="n">
-        <v>1870.1</v>
+        <v>1791.6</v>
       </c>
       <c r="AX13" t="n">
-        <v>1870.1</v>
+        <v>1791.6</v>
       </c>
       <c r="AY13" t="n">
-        <v>1870.1</v>
+        <v>1791.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1870.1</v>
+        <v>1791.6</v>
       </c>
       <c r="BA13" t="n">
-        <v>1870.1</v>
+        <v>1791.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>1870.1</v>
+        <v>1791.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>1870.1</v>
+        <v>1791.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>1870.1</v>
+        <v>1791.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>1870.1</v>
+        <v>1791.6</v>
       </c>
       <c r="BF13" t="n">
-        <v>1870.1</v>
+        <v>1791.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>1870.1</v>
+        <v>1791.6</v>
       </c>
       <c r="BH13" t="n">
-        <v>1870.1</v>
+        <v>1791.6</v>
       </c>
       <c r="BI13" t="n">
-        <v>1870.1</v>
+        <v>1791.6</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1870.1</v>
+        <v>1791.6</v>
       </c>
       <c r="BK13" t="n">
-        <v>1870.1</v>
+        <v>1791.6</v>
       </c>
       <c r="BL13" t="n">
-        <v>1870.1</v>
+        <v>1791.6</v>
       </c>
       <c r="BM13" t="n">
-        <v>1870.1</v>
+        <v>1791.6</v>
       </c>
       <c r="BN13" t="n">
-        <v>1870.1</v>
+        <v>1791.6</v>
       </c>
       <c r="BO13" t="n">
-        <v>1870.1</v>
+        <v>1791.6</v>
       </c>
       <c r="BP13" t="n">
-        <v>1870.1</v>
+        <v>1791.6</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1870.1</v>
+        <v>1791.6</v>
       </c>
       <c r="BR13" t="n">
-        <v>1870.1</v>
+        <v>1791.6</v>
       </c>
       <c r="BS13" t="n">
-        <v>1870.1</v>
+        <v>1791.6</v>
       </c>
       <c r="BT13" t="n">
-        <v>1870.1</v>
+        <v>1791.6</v>
       </c>
       <c r="BU13" t="n">
-        <v>1870.1</v>
+        <v>1791.6</v>
       </c>
       <c r="BV13" t="n">
-        <v>1870.1</v>
+        <v>1791.6</v>
       </c>
       <c r="BW13" t="n">
-        <v>1870.1</v>
+        <v>1791.6</v>
       </c>
       <c r="BX13" t="n">
-        <v>1870.1</v>
+        <v>1791.6</v>
       </c>
       <c r="BY13" t="n">
-        <v>1870.1</v>
+        <v>1791.6</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1870.1</v>
+        <v>1791.6</v>
       </c>
     </row>
     <row r="14">
@@ -36176,235 +36176,235 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="F14" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="G14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="K14" t="n">
         <v>10</v>
       </c>
-      <c r="C14" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="D14" t="n">
+      <c r="L14" t="n">
         <v>10.4</v>
       </c>
-      <c r="E14" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="F14" t="n">
+      <c r="M14" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="N14" t="n">
         <v>10.9</v>
       </c>
-      <c r="G14" t="n">
+      <c r="O14" t="n">
         <v>11.1</v>
       </c>
-      <c r="H14" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="I14" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="K14" t="n">
+      <c r="P14" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="R14" t="n">
         <v>12</v>
       </c>
-      <c r="L14" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="M14" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="N14" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="O14" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="P14" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="R14" t="n">
-        <v>14</v>
-      </c>
       <c r="S14" t="n">
-        <v>14.2</v>
+        <v>12.2</v>
       </c>
       <c r="T14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="V14" t="n">
+        <v>13</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="AA14" t="n">
         <v>14.4</v>
       </c>
-      <c r="U14" t="n">
+      <c r="AB14" t="n">
         <v>14.7</v>
       </c>
-      <c r="V14" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="W14" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="X14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="Z14" t="n">
+      <c r="AC14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="AF14" t="n">
         <v>16.1</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AG14" t="n">
         <v>16.4</v>
       </c>
-      <c r="AB14" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>18.4</v>
-      </c>
       <c r="AH14" t="n">
-        <v>18.8</v>
+        <v>16.8</v>
       </c>
       <c r="AI14" t="n">
-        <v>19.2</v>
+        <v>17.2</v>
       </c>
       <c r="AJ14" t="n">
-        <v>19.6</v>
+        <v>17.6</v>
       </c>
       <c r="AK14" t="n">
-        <v>20</v>
+        <v>18.1</v>
       </c>
       <c r="AL14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="AM14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="AN14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="AO14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="AP14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="AR14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="AS14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="AT14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="AU14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="AV14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="AW14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="AX14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="AY14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="AZ14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="BA14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="BB14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="BC14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="BD14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="BE14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="BF14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="BG14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="BH14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="BI14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="BJ14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="BK14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="BL14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="BM14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="BN14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="BO14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="BP14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="BQ14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="BR14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="BS14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="BT14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="BU14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="BV14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="BW14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="BX14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="BY14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
       <c r="BZ14" t="n">
-        <v>20.3</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="15">
@@ -36414,235 +36414,235 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>985</v>
+        <v>799.4</v>
       </c>
       <c r="C15" t="n">
-        <v>998.8</v>
+        <v>813.2</v>
       </c>
       <c r="D15" t="n">
-        <v>1014.9</v>
+        <v>829.3</v>
       </c>
       <c r="E15" t="n">
-        <v>1031.2</v>
+        <v>845.6</v>
       </c>
       <c r="F15" t="n">
-        <v>1047.8</v>
+        <v>862.2</v>
       </c>
       <c r="G15" t="n">
-        <v>1064.7</v>
+        <v>879.1</v>
       </c>
       <c r="H15" t="n">
-        <v>1079</v>
+        <v>893.4</v>
       </c>
       <c r="I15" t="n">
-        <v>1096.3</v>
+        <v>910.8</v>
       </c>
       <c r="J15" t="n">
-        <v>1114</v>
+        <v>928.4</v>
       </c>
       <c r="K15" t="n">
-        <v>1123.1</v>
+        <v>937.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1150.5</v>
+        <v>965</v>
       </c>
       <c r="M15" t="n">
-        <v>1166</v>
+        <v>980.4</v>
       </c>
       <c r="N15" t="n">
-        <v>1185.5</v>
+        <v>999.9</v>
       </c>
       <c r="O15" t="n">
-        <v>1205.7</v>
+        <v>1020.1</v>
       </c>
       <c r="P15" t="n">
-        <v>1226.7</v>
+        <v>1041.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>1248.6</v>
+        <v>1063</v>
       </c>
       <c r="R15" t="n">
-        <v>1266.8</v>
+        <v>1081.2</v>
       </c>
       <c r="S15" t="n">
-        <v>1283.1</v>
+        <v>1097.5</v>
       </c>
       <c r="T15" t="n">
-        <v>1300.2</v>
+        <v>1114.6</v>
       </c>
       <c r="U15" t="n">
-        <v>1317.7</v>
+        <v>1132.2</v>
       </c>
       <c r="V15" t="n">
-        <v>1335.9</v>
+        <v>1150.3</v>
       </c>
       <c r="W15" t="n">
-        <v>1354.7</v>
+        <v>1169.1</v>
       </c>
       <c r="X15" t="n">
-        <v>1374.1</v>
+        <v>1188.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>1394.2</v>
+        <v>1208.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>1415</v>
+        <v>1229.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>1436.5</v>
+        <v>1250.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>1458.8</v>
+        <v>1273.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>1482</v>
+        <v>1296.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1505.9</v>
+        <v>1320.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1530.8</v>
+        <v>1345.2</v>
       </c>
       <c r="AF15" t="n">
-        <v>1556.5</v>
+        <v>1370.9</v>
       </c>
       <c r="AG15" t="n">
-        <v>1583.2</v>
+        <v>1397.6</v>
       </c>
       <c r="AH15" t="n">
-        <v>1610.8</v>
+        <v>1425.2</v>
       </c>
       <c r="AI15" t="n">
-        <v>1639.5</v>
+        <v>1453.9</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1668.9</v>
+        <v>1483.4</v>
       </c>
       <c r="AK15" t="n">
-        <v>1699.1</v>
+        <v>1513.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>1804.1</v>
+        <v>1618.5</v>
       </c>
       <c r="AM15" t="n">
-        <v>1936.8</v>
+        <v>1751.2</v>
       </c>
       <c r="AN15" t="n">
-        <v>2125.6</v>
+        <v>1940</v>
       </c>
       <c r="AO15" t="n">
-        <v>2318.8</v>
+        <v>2133.3</v>
       </c>
       <c r="AP15" t="n">
-        <v>2516.7</v>
+        <v>2331.2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3415.4</v>
+        <v>3229.9</v>
       </c>
       <c r="AR15" t="n">
-        <v>4336.8</v>
+        <v>4151.2</v>
       </c>
       <c r="AS15" t="n">
-        <v>5280.3</v>
+        <v>5094.7</v>
       </c>
       <c r="AT15" t="n">
-        <v>6246.4</v>
+        <v>6060.8</v>
       </c>
       <c r="AU15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
       <c r="AV15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
       <c r="AW15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
       <c r="AX15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
       <c r="AY15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
       <c r="BA15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
       <c r="BB15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
       <c r="BC15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
       <c r="BD15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
       <c r="BE15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
       <c r="BF15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
       <c r="BG15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
       <c r="BH15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
       <c r="BI15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
       <c r="BJ15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
       <c r="BK15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
       <c r="BL15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
       <c r="BM15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
       <c r="BN15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
       <c r="BO15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
       <c r="BP15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
       <c r="BR15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
       <c r="BS15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
       <c r="BT15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
       <c r="BU15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
       <c r="BV15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
       <c r="BW15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
       <c r="BX15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
       <c r="BY15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
       <c r="BZ15" t="n">
-        <v>6923.7</v>
+        <v>6738.1</v>
       </c>
     </row>
     <row r="16">
@@ -36652,235 +36652,235 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>380.9</v>
+        <v>438.1</v>
       </c>
       <c r="C16" t="n">
-        <v>391.4</v>
+        <v>448.6</v>
       </c>
       <c r="D16" t="n">
-        <v>403.7</v>
+        <v>460.9</v>
       </c>
       <c r="E16" t="n">
-        <v>416.2</v>
+        <v>473.3</v>
       </c>
       <c r="F16" t="n">
-        <v>428.8</v>
+        <v>486</v>
       </c>
       <c r="G16" t="n">
-        <v>441.7</v>
+        <v>498.9</v>
       </c>
       <c r="H16" t="n">
-        <v>452.7</v>
+        <v>509.8</v>
       </c>
       <c r="I16" t="n">
-        <v>465.9</v>
+        <v>523.1</v>
       </c>
       <c r="J16" t="n">
-        <v>479.4</v>
+        <v>536.6</v>
       </c>
       <c r="K16" t="n">
-        <v>486.3</v>
+        <v>543.5</v>
       </c>
       <c r="L16" t="n">
-        <v>507.3</v>
+        <v>564.5</v>
       </c>
       <c r="M16" t="n">
-        <v>519.1</v>
+        <v>576.3</v>
       </c>
       <c r="N16" t="n">
-        <v>534</v>
+        <v>591.1</v>
       </c>
       <c r="O16" t="n">
-        <v>549.4</v>
+        <v>606.6</v>
       </c>
       <c r="P16" t="n">
-        <v>565.5</v>
+        <v>622.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>582.2</v>
+        <v>639.3</v>
       </c>
       <c r="R16" t="n">
-        <v>596.1</v>
+        <v>653.3</v>
       </c>
       <c r="S16" t="n">
-        <v>608.5</v>
+        <v>665.7</v>
       </c>
       <c r="T16" t="n">
-        <v>621.6</v>
+        <v>678.7</v>
       </c>
       <c r="U16" t="n">
-        <v>635</v>
+        <v>692.2</v>
       </c>
       <c r="V16" t="n">
-        <v>648.9</v>
+        <v>706.1</v>
       </c>
       <c r="W16" t="n">
-        <v>663.2</v>
+        <v>720.4</v>
       </c>
       <c r="X16" t="n">
-        <v>678</v>
+        <v>735.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>693.4</v>
+        <v>750.6</v>
       </c>
       <c r="Z16" t="n">
-        <v>709.3</v>
+        <v>766.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>725.7</v>
+        <v>782.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>742.8</v>
+        <v>800</v>
       </c>
       <c r="AC16" t="n">
-        <v>760.5</v>
+        <v>817.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="AJ16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="AK16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="AM16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="AN16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="BF16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="BH16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="BI16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="BJ16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="BL16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="BM16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="BN16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="BO16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="BP16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="BR16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="BS16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="BT16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="BU16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="BV16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="BW16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="BX16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="BY16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
       <c r="BZ16" t="n">
-        <v>762.3</v>
+        <v>819.5</v>
       </c>
     </row>
     <row r="17">
@@ -36890,235 +36890,235 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>320.7</v>
+        <v>241.2</v>
       </c>
       <c r="C17" t="n">
-        <v>326.5</v>
+        <v>246.9</v>
       </c>
       <c r="D17" t="n">
-        <v>333.3</v>
+        <v>253.7</v>
       </c>
       <c r="E17" t="n">
-        <v>340.2</v>
+        <v>260.6</v>
       </c>
       <c r="F17" t="n">
-        <v>347.1</v>
+        <v>267.6</v>
       </c>
       <c r="G17" t="n">
-        <v>354.2</v>
+        <v>274.7</v>
       </c>
       <c r="H17" t="n">
-        <v>360.3</v>
+        <v>280.7</v>
       </c>
       <c r="I17" t="n">
-        <v>367.5</v>
+        <v>288</v>
       </c>
       <c r="J17" t="n">
-        <v>375</v>
+        <v>295.4</v>
       </c>
       <c r="K17" t="n">
-        <v>378.8</v>
+        <v>299.2</v>
       </c>
       <c r="L17" t="n">
-        <v>390.3</v>
+        <v>310.8</v>
       </c>
       <c r="M17" t="n">
-        <v>396.8</v>
+        <v>317.2</v>
       </c>
       <c r="N17" t="n">
-        <v>405</v>
+        <v>325.4</v>
       </c>
       <c r="O17" t="n">
-        <v>413.5</v>
+        <v>333.9</v>
       </c>
       <c r="P17" t="n">
-        <v>422.3</v>
+        <v>342.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>431.5</v>
+        <v>352</v>
       </c>
       <c r="R17" t="n">
-        <v>439.2</v>
+        <v>359.6</v>
       </c>
       <c r="S17" t="n">
-        <v>446.1</v>
+        <v>366.5</v>
       </c>
       <c r="T17" t="n">
-        <v>453.2</v>
+        <v>373.7</v>
       </c>
       <c r="U17" t="n">
-        <v>460.6</v>
+        <v>381</v>
       </c>
       <c r="V17" t="n">
-        <v>468.3</v>
+        <v>388.7</v>
       </c>
       <c r="W17" t="n">
-        <v>476.2</v>
+        <v>396.6</v>
       </c>
       <c r="X17" t="n">
-        <v>484.3</v>
+        <v>404.7</v>
       </c>
       <c r="Y17" t="n">
-        <v>492.8</v>
+        <v>413.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>501.5</v>
+        <v>421.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>510.6</v>
+        <v>431</v>
       </c>
       <c r="AB17" t="n">
-        <v>520</v>
+        <v>440.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>529.7</v>
+        <v>450.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>539.8</v>
+        <v>460.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="AF17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="AH17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="AI17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="AJ17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="AK17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="AL17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="AM17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="AN17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="AO17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="AP17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="AR17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="AS17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="AT17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="AW17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="AX17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="AY17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="AZ17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="BA17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="BB17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="BC17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="BD17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="BF17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="BH17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="BI17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="BJ17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="BK17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="BL17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="BM17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="BN17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="BO17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="BP17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="BQ17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="BR17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="BS17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="BT17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="BU17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="BV17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="BW17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="BX17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="BY17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
       <c r="BZ17" t="n">
-        <v>541.4</v>
+        <v>461.8</v>
       </c>
     </row>
     <row r="18">
@@ -37128,235 +37128,235 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10070.7</v>
+        <v>11492.4</v>
       </c>
       <c r="C18" t="n">
-        <v>10346</v>
+        <v>11767.7</v>
       </c>
       <c r="D18" t="n">
-        <v>10668.7</v>
+        <v>12090.4</v>
       </c>
       <c r="E18" t="n">
-        <v>10996</v>
+        <v>12417.7</v>
       </c>
       <c r="F18" t="n">
-        <v>11328.7</v>
+        <v>12750.4</v>
       </c>
       <c r="G18" t="n">
-        <v>11667.1</v>
+        <v>13088.7</v>
       </c>
       <c r="H18" t="n">
-        <v>11953.4</v>
+        <v>13375.1</v>
       </c>
       <c r="I18" t="n">
-        <v>12300.8</v>
+        <v>13722.5</v>
       </c>
       <c r="J18" t="n">
-        <v>12654.8</v>
+        <v>14076.4</v>
       </c>
       <c r="K18" t="n">
-        <v>12836.1</v>
+        <v>14257.7</v>
       </c>
       <c r="L18" t="n">
-        <v>13386.7</v>
+        <v>14808.3</v>
       </c>
       <c r="M18" t="n">
-        <v>13695.5</v>
+        <v>15117.2</v>
       </c>
       <c r="N18" t="n">
-        <v>14086</v>
+        <v>15507.7</v>
       </c>
       <c r="O18" t="n">
-        <v>14492</v>
+        <v>15913.6</v>
       </c>
       <c r="P18" t="n">
-        <v>14912.2</v>
+        <v>16333.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>15350.4</v>
+        <v>16772.1</v>
       </c>
       <c r="R18" t="n">
-        <v>15715.2</v>
+        <v>17136.9</v>
       </c>
       <c r="S18" t="n">
-        <v>16042.1</v>
+        <v>17463.8</v>
       </c>
       <c r="T18" t="n">
-        <v>16383.9</v>
+        <v>17805.6</v>
       </c>
       <c r="U18" t="n">
-        <v>16736.4</v>
+        <v>18158.1</v>
       </c>
       <c r="V18" t="n">
-        <v>17100.3</v>
+        <v>18521.9</v>
       </c>
       <c r="W18" t="n">
-        <v>17476.2</v>
+        <v>18897.8</v>
       </c>
       <c r="X18" t="n">
-        <v>17865</v>
+        <v>19286.6</v>
       </c>
       <c r="Y18" t="n">
-        <v>18267.3</v>
+        <v>19689</v>
       </c>
       <c r="Z18" t="n">
-        <v>18684</v>
+        <v>20105.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>19115.7</v>
+        <v>20537.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>19563.2</v>
+        <v>20984.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>20026.7</v>
+        <v>21448.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>20506.9</v>
+        <v>21928.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>21004.4</v>
+        <v>22426</v>
       </c>
       <c r="AF18" t="n">
-        <v>21519.9</v>
+        <v>22941.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>22054.2</v>
+        <v>23475.8</v>
       </c>
       <c r="AH18" t="n">
-        <v>22607.9</v>
+        <v>24029.6</v>
       </c>
       <c r="AI18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="AK18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="AL18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="AM18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="AN18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="AO18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="AP18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="AT18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="AV18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="BH18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="BI18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="BJ18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="BL18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="BM18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="BN18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="BO18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="BP18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="BR18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="BS18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="BT18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="BU18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="BV18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="BW18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="BX18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="BY18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
       <c r="BZ18" t="n">
-        <v>22625.8</v>
+        <v>24047.5</v>
       </c>
     </row>
     <row r="19">
@@ -37366,235 +37366,235 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="C19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="D19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="E19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="F19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="G19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="H19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="I19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="J19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="K19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="L19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="N19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="R19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="S19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="T19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="U19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="V19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="W19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="X19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AF19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AI19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AJ19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AK19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AL19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AM19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AN19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AO19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AP19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AR19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AS19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AW19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AX19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AY19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BA19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BB19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BH19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BJ19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BK19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BL19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BM19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BN19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BQ19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BR19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BS19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BT19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BU19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BV19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BW19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BX19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BY19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BZ19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="20">
@@ -37604,235 +37604,235 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24.6</v>
+        <v>28.3</v>
       </c>
       <c r="C20" t="n">
-        <v>25.3</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>26.1</v>
+        <v>29.8</v>
       </c>
       <c r="E20" t="n">
-        <v>26.9</v>
+        <v>30.6</v>
       </c>
       <c r="F20" t="n">
-        <v>27.7</v>
+        <v>31.4</v>
       </c>
       <c r="G20" t="n">
-        <v>28.5</v>
+        <v>32.2</v>
       </c>
       <c r="H20" t="n">
-        <v>29.2</v>
+        <v>32.9</v>
       </c>
       <c r="I20" t="n">
-        <v>30.1</v>
+        <v>33.8</v>
       </c>
       <c r="J20" t="n">
-        <v>31</v>
+        <v>34.7</v>
       </c>
       <c r="K20" t="n">
-        <v>31.4</v>
+        <v>35.1</v>
       </c>
       <c r="L20" t="n">
-        <v>32.8</v>
+        <v>36.5</v>
       </c>
       <c r="M20" t="n">
-        <v>33.5</v>
+        <v>37.2</v>
       </c>
       <c r="N20" t="n">
-        <v>34.5</v>
+        <v>38.2</v>
       </c>
       <c r="O20" t="n">
-        <v>35.5</v>
+        <v>39.2</v>
       </c>
       <c r="P20" t="n">
-        <v>36.5</v>
+        <v>40.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>37.6</v>
+        <v>41.3</v>
       </c>
       <c r="R20" t="n">
-        <v>38.5</v>
+        <v>42.2</v>
       </c>
       <c r="S20" t="n">
-        <v>39.3</v>
+        <v>43</v>
       </c>
       <c r="T20" t="n">
-        <v>40.1</v>
+        <v>43.8</v>
       </c>
       <c r="U20" t="n">
-        <v>41</v>
+        <v>44.7</v>
       </c>
       <c r="V20" t="n">
-        <v>41.9</v>
+        <v>45.6</v>
       </c>
       <c r="W20" t="n">
-        <v>42.8</v>
+        <v>46.5</v>
       </c>
       <c r="X20" t="n">
-        <v>43.8</v>
+        <v>47.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>44.8</v>
+        <v>48.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>45.8</v>
+        <v>49.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>46.8</v>
+        <v>50.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>47.9</v>
+        <v>51.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>49.1</v>
+        <v>52.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>50.3</v>
+        <v>54</v>
       </c>
       <c r="AE20" t="n">
-        <v>51.5</v>
+        <v>55.2</v>
       </c>
       <c r="AF20" t="n">
-        <v>52.8</v>
+        <v>56.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>54.1</v>
+        <v>57.8</v>
       </c>
       <c r="AH20" t="n">
-        <v>55.4</v>
+        <v>59.1</v>
       </c>
       <c r="AI20" t="n">
-        <v>56.8</v>
+        <v>60.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>58.3</v>
+        <v>62</v>
       </c>
       <c r="AK20" t="n">
-        <v>59.8</v>
+        <v>63.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>103.3</v>
+        <v>107</v>
       </c>
       <c r="AM20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="AN20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="AO20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="AP20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="AQ20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="AR20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="AS20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="AT20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="AU20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="AV20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="AW20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="AX20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="AY20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="AZ20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="BA20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="BB20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="BC20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="BD20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="BE20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="BF20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="BG20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="BH20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="BI20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="BJ20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="BK20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="BL20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="BM20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="BN20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="BO20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="BP20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="BQ20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="BR20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="BS20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="BT20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="BU20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="BV20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="BW20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="BX20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="BY20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
       <c r="BZ20" t="n">
-        <v>126.2</v>
+        <v>129.9</v>
       </c>
     </row>
     <row r="21">
@@ -37842,235 +37842,235 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>416.4</v>
+        <v>313.1</v>
       </c>
       <c r="C21" t="n">
-        <v>423.9</v>
+        <v>320.6</v>
       </c>
       <c r="D21" t="n">
-        <v>432.7</v>
+        <v>329.4</v>
       </c>
       <c r="E21" t="n">
-        <v>441.6</v>
+        <v>338.3</v>
       </c>
       <c r="F21" t="n">
-        <v>450.7</v>
+        <v>347.4</v>
       </c>
       <c r="G21" t="n">
-        <v>459.9</v>
+        <v>356.6</v>
       </c>
       <c r="H21" t="n">
-        <v>467.7</v>
+        <v>364.4</v>
       </c>
       <c r="I21" t="n">
-        <v>477.2</v>
+        <v>373.9</v>
       </c>
       <c r="J21" t="n">
-        <v>486.8</v>
+        <v>383.5</v>
       </c>
       <c r="K21" t="n">
-        <v>491.8</v>
+        <v>388.4</v>
       </c>
       <c r="L21" t="n">
-        <v>506.8</v>
+        <v>403.4</v>
       </c>
       <c r="M21" t="n">
-        <v>515.2</v>
+        <v>411.9</v>
       </c>
       <c r="N21" t="n">
-        <v>525.8</v>
+        <v>422.5</v>
       </c>
       <c r="O21" t="n">
-        <v>536.9</v>
+        <v>433.6</v>
       </c>
       <c r="P21" t="n">
-        <v>548.3</v>
+        <v>445</v>
       </c>
       <c r="Q21" t="n">
-        <v>560.3</v>
+        <v>457</v>
       </c>
       <c r="R21" t="n">
-        <v>570.2</v>
+        <v>466.9</v>
       </c>
       <c r="S21" t="n">
-        <v>579.1</v>
+        <v>475.8</v>
       </c>
       <c r="T21" t="n">
-        <v>588.4</v>
+        <v>485.1</v>
       </c>
       <c r="U21" t="n">
-        <v>598</v>
+        <v>494.7</v>
       </c>
       <c r="V21" t="n">
-        <v>607.9</v>
+        <v>504.6</v>
       </c>
       <c r="W21" t="n">
-        <v>618.2</v>
+        <v>514.9</v>
       </c>
       <c r="X21" t="n">
-        <v>628.8</v>
+        <v>525.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>639.7</v>
+        <v>536.4</v>
       </c>
       <c r="Z21" t="n">
-        <v>651.1</v>
+        <v>547.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>662.9</v>
+        <v>559.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>675.1</v>
+        <v>571.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>687.7</v>
+        <v>584.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>700.8</v>
+        <v>597.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>714.3</v>
+        <v>611</v>
       </c>
       <c r="AF21" t="n">
-        <v>728.4</v>
+        <v>625</v>
       </c>
       <c r="AG21" t="n">
-        <v>742.9</v>
+        <v>639.6</v>
       </c>
       <c r="AH21" t="n">
-        <v>758</v>
+        <v>654.7</v>
       </c>
       <c r="AI21" t="n">
-        <v>773.6</v>
+        <v>670.3</v>
       </c>
       <c r="AJ21" t="n">
-        <v>789.7</v>
+        <v>686.4</v>
       </c>
       <c r="AK21" t="n">
-        <v>806.2</v>
+        <v>702.9</v>
       </c>
       <c r="AL21" t="n">
-        <v>823.1</v>
+        <v>719.8</v>
       </c>
       <c r="AM21" t="n">
-        <v>840.3</v>
+        <v>737</v>
       </c>
       <c r="AN21" t="n">
-        <v>858</v>
+        <v>754.7</v>
       </c>
       <c r="AO21" t="n">
-        <v>876.2</v>
+        <v>772.8</v>
       </c>
       <c r="AP21" t="n">
-        <v>894.7</v>
+        <v>791.4</v>
       </c>
       <c r="AQ21" t="n">
-        <v>917</v>
+        <v>813.6</v>
       </c>
       <c r="AR21" t="n">
-        <v>939.8</v>
+        <v>836.4</v>
       </c>
       <c r="AS21" t="n">
-        <v>963.1</v>
+        <v>859.8</v>
       </c>
       <c r="AT21" t="n">
-        <v>987</v>
+        <v>883.7</v>
       </c>
       <c r="AU21" t="n">
-        <v>1011.5</v>
+        <v>908.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>1170.2</v>
+        <v>1066.9</v>
       </c>
       <c r="AW21" t="n">
-        <v>2101</v>
+        <v>1997.7</v>
       </c>
       <c r="AX21" t="n">
-        <v>2621.2</v>
+        <v>2517.8</v>
       </c>
       <c r="AY21" t="n">
-        <v>2621.2</v>
+        <v>2517.8</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2621.2</v>
+        <v>2517.8</v>
       </c>
       <c r="BA21" t="n">
-        <v>2621.2</v>
+        <v>2517.8</v>
       </c>
       <c r="BB21" t="n">
-        <v>2621.2</v>
+        <v>2517.8</v>
       </c>
       <c r="BC21" t="n">
-        <v>2621.2</v>
+        <v>2517.8</v>
       </c>
       <c r="BD21" t="n">
-        <v>2621.2</v>
+        <v>2517.8</v>
       </c>
       <c r="BE21" t="n">
-        <v>2621.2</v>
+        <v>2517.8</v>
       </c>
       <c r="BF21" t="n">
-        <v>2621.2</v>
+        <v>2517.8</v>
       </c>
       <c r="BG21" t="n">
-        <v>2621.2</v>
+        <v>2517.8</v>
       </c>
       <c r="BH21" t="n">
-        <v>2621.2</v>
+        <v>2517.8</v>
       </c>
       <c r="BI21" t="n">
-        <v>2621.2</v>
+        <v>2517.8</v>
       </c>
       <c r="BJ21" t="n">
-        <v>2621.2</v>
+        <v>2517.8</v>
       </c>
       <c r="BK21" t="n">
-        <v>2621.2</v>
+        <v>2517.8</v>
       </c>
       <c r="BL21" t="n">
-        <v>2621.2</v>
+        <v>2517.8</v>
       </c>
       <c r="BM21" t="n">
-        <v>2621.2</v>
+        <v>2517.8</v>
       </c>
       <c r="BN21" t="n">
-        <v>2621.2</v>
+        <v>2517.8</v>
       </c>
       <c r="BO21" t="n">
-        <v>2621.2</v>
+        <v>2517.8</v>
       </c>
       <c r="BP21" t="n">
-        <v>2621.2</v>
+        <v>2517.8</v>
       </c>
       <c r="BQ21" t="n">
-        <v>2621.2</v>
+        <v>2517.8</v>
       </c>
       <c r="BR21" t="n">
-        <v>2621.2</v>
+        <v>2517.8</v>
       </c>
       <c r="BS21" t="n">
-        <v>2621.2</v>
+        <v>2517.8</v>
       </c>
       <c r="BT21" t="n">
-        <v>2621.2</v>
+        <v>2517.8</v>
       </c>
       <c r="BU21" t="n">
-        <v>2621.2</v>
+        <v>2517.8</v>
       </c>
       <c r="BV21" t="n">
-        <v>2621.2</v>
+        <v>2517.8</v>
       </c>
       <c r="BW21" t="n">
-        <v>2621.2</v>
+        <v>2517.8</v>
       </c>
       <c r="BX21" t="n">
-        <v>2621.2</v>
+        <v>2517.8</v>
       </c>
       <c r="BY21" t="n">
-        <v>2621.2</v>
+        <v>2517.8</v>
       </c>
       <c r="BZ21" t="n">
-        <v>2621.2</v>
+        <v>2517.8</v>
       </c>
     </row>
     <row r="22">
@@ -38080,235 +38080,235 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>34.6</v>
+        <v>26</v>
       </c>
       <c r="C22" t="n">
-        <v>35.2</v>
+        <v>26.7</v>
       </c>
       <c r="D22" t="n">
-        <v>36</v>
+        <v>27.4</v>
       </c>
       <c r="E22" t="n">
-        <v>36.7</v>
+        <v>28.1</v>
       </c>
       <c r="F22" t="n">
-        <v>37.5</v>
+        <v>28.9</v>
       </c>
       <c r="G22" t="n">
-        <v>38.2</v>
+        <v>29.7</v>
       </c>
       <c r="H22" t="n">
-        <v>38.9</v>
+        <v>30.3</v>
       </c>
       <c r="I22" t="n">
-        <v>39.7</v>
+        <v>31.1</v>
       </c>
       <c r="J22" t="n">
-        <v>40.5</v>
+        <v>31.9</v>
       </c>
       <c r="K22" t="n">
-        <v>40.9</v>
+        <v>32.3</v>
       </c>
       <c r="L22" t="n">
-        <v>42.1</v>
+        <v>33.5</v>
       </c>
       <c r="M22" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="N22" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>38</v>
+      </c>
+      <c r="R22" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="S22" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="T22" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="V22" t="n">
+        <v>42</v>
+      </c>
+      <c r="W22" t="n">
         <v>42.8</v>
       </c>
-      <c r="N22" t="n">
+      <c r="X22" t="n">
         <v>43.7</v>
       </c>
-      <c r="O22" t="n">
+      <c r="Y22" t="n">
         <v>44.6</v>
       </c>
-      <c r="P22" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="R22" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="S22" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="U22" t="n">
+      <c r="Z22" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="AD22" t="n">
         <v>49.7</v>
       </c>
-      <c r="V22" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="W22" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="X22" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="Y22" t="n">
+      <c r="AE22" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>52</v>
+      </c>
+      <c r="AG22" t="n">
         <v>53.2</v>
       </c>
-      <c r="Z22" t="n">
-        <v>54.1</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>61.8</v>
-      </c>
       <c r="AH22" t="n">
-        <v>63</v>
+        <v>54.4</v>
       </c>
       <c r="AI22" t="n">
-        <v>300.9</v>
+        <v>292.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>567.9</v>
+        <v>559.3</v>
       </c>
       <c r="AK22" t="n">
-        <v>841.4</v>
+        <v>832.8</v>
       </c>
       <c r="AL22" t="n">
-        <v>1208.3</v>
+        <v>1199.7</v>
       </c>
       <c r="AM22" t="n">
-        <v>1849.3</v>
+        <v>1840.7</v>
       </c>
       <c r="AN22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="AO22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="AP22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="AQ22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="AR22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="AS22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="AT22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="AU22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="AW22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="AX22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="AY22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="BA22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="BB22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="BC22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="BD22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="BH22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="BI22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="BJ22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="BK22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="BL22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="BM22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="BN22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="BO22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="BP22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="BQ22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="BR22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="BS22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="BT22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="BU22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="BV22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="BW22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="BX22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="BY22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
       <c r="BZ22" t="n">
-        <v>2283.2</v>
+        <v>2274.6</v>
       </c>
     </row>
     <row r="23">
@@ -38318,235 +38318,235 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>274.3</v>
+        <v>267</v>
       </c>
       <c r="C23" t="n">
-        <v>280.7</v>
+        <v>273.4</v>
       </c>
       <c r="D23" t="n">
-        <v>288.2</v>
+        <v>280.9</v>
       </c>
       <c r="E23" t="n">
-        <v>295.8</v>
+        <v>288.5</v>
       </c>
       <c r="F23" t="n">
-        <v>303.5</v>
+        <v>296.2</v>
       </c>
       <c r="G23" t="n">
-        <v>311.4</v>
+        <v>304.1</v>
       </c>
       <c r="H23" t="n">
-        <v>318</v>
+        <v>310.8</v>
       </c>
       <c r="I23" t="n">
-        <v>326.1</v>
+        <v>318.8</v>
       </c>
       <c r="J23" t="n">
-        <v>334.3</v>
+        <v>327.1</v>
       </c>
       <c r="K23" t="n">
-        <v>338.5</v>
+        <v>331.3</v>
       </c>
       <c r="L23" t="n">
-        <v>351.3</v>
+        <v>344.1</v>
       </c>
       <c r="M23" t="n">
-        <v>358.5</v>
+        <v>351.2</v>
       </c>
       <c r="N23" t="n">
-        <v>367.6</v>
+        <v>360.3</v>
       </c>
       <c r="O23" t="n">
-        <v>377</v>
+        <v>369.7</v>
       </c>
       <c r="P23" t="n">
-        <v>386.8</v>
+        <v>379.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>397</v>
+        <v>389.7</v>
       </c>
       <c r="R23" t="n">
-        <v>405.4</v>
+        <v>398.2</v>
       </c>
       <c r="S23" t="n">
-        <v>413</v>
+        <v>405.8</v>
       </c>
       <c r="T23" t="n">
-        <v>421</v>
+        <v>413.7</v>
       </c>
       <c r="U23" t="n">
-        <v>429.2</v>
+        <v>421.9</v>
       </c>
       <c r="V23" t="n">
-        <v>437.6</v>
+        <v>430.3</v>
       </c>
       <c r="W23" t="n">
-        <v>446.3</v>
+        <v>439.1</v>
       </c>
       <c r="X23" t="n">
-        <v>455.4</v>
+        <v>448.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>464.7</v>
+        <v>457.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>474.4</v>
+        <v>467.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>484.4</v>
+        <v>477.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>494.8</v>
+        <v>487.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>505.6</v>
+        <v>498.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>516.8</v>
+        <v>509.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>528.3</v>
+        <v>521.1</v>
       </c>
       <c r="AF23" t="n">
-        <v>540.3</v>
+        <v>533</v>
       </c>
       <c r="AG23" t="n">
-        <v>552.7</v>
+        <v>545.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>565.6</v>
+        <v>558.3</v>
       </c>
       <c r="AI23" t="n">
-        <v>578.9</v>
+        <v>571.7</v>
       </c>
       <c r="AJ23" t="n">
-        <v>592.6</v>
+        <v>585.4</v>
       </c>
       <c r="AK23" t="n">
-        <v>606.7</v>
+        <v>599.4</v>
       </c>
       <c r="AL23" t="n">
-        <v>621.1</v>
+        <v>613.8</v>
       </c>
       <c r="AM23" t="n">
-        <v>635.8</v>
+        <v>628.5</v>
       </c>
       <c r="AN23" t="n">
-        <v>650.9</v>
+        <v>643.6</v>
       </c>
       <c r="AO23" t="n">
-        <v>666.3</v>
+        <v>659.1</v>
       </c>
       <c r="AP23" t="n">
-        <v>682.2</v>
+        <v>674.9</v>
       </c>
       <c r="AQ23" t="n">
-        <v>698.4</v>
+        <v>691.1</v>
       </c>
       <c r="AR23" t="n">
-        <v>715</v>
+        <v>707.7</v>
       </c>
       <c r="AS23" t="n">
-        <v>731.9</v>
+        <v>724.7</v>
       </c>
       <c r="AT23" t="n">
-        <v>749.3</v>
+        <v>742.1</v>
       </c>
       <c r="AU23" t="n">
-        <v>767.1</v>
+        <v>759.9</v>
       </c>
       <c r="AV23" t="n">
-        <v>785.4</v>
+        <v>778.1</v>
       </c>
       <c r="AW23" t="n">
-        <v>842.4</v>
+        <v>835.1</v>
       </c>
       <c r="AX23" t="n">
-        <v>1186.3</v>
+        <v>1179</v>
       </c>
       <c r="AY23" t="n">
-        <v>1365.2</v>
+        <v>1357.9</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1365.2</v>
+        <v>1357.9</v>
       </c>
       <c r="BA23" t="n">
-        <v>1365.2</v>
+        <v>1357.9</v>
       </c>
       <c r="BB23" t="n">
-        <v>1365.2</v>
+        <v>1357.9</v>
       </c>
       <c r="BC23" t="n">
-        <v>1365.2</v>
+        <v>1357.9</v>
       </c>
       <c r="BD23" t="n">
-        <v>1365.2</v>
+        <v>1357.9</v>
       </c>
       <c r="BE23" t="n">
-        <v>1365.2</v>
+        <v>1357.9</v>
       </c>
       <c r="BF23" t="n">
-        <v>1365.2</v>
+        <v>1357.9</v>
       </c>
       <c r="BG23" t="n">
-        <v>1365.2</v>
+        <v>1357.9</v>
       </c>
       <c r="BH23" t="n">
-        <v>1365.2</v>
+        <v>1357.9</v>
       </c>
       <c r="BI23" t="n">
-        <v>1365.2</v>
+        <v>1357.9</v>
       </c>
       <c r="BJ23" t="n">
-        <v>1365.2</v>
+        <v>1357.9</v>
       </c>
       <c r="BK23" t="n">
-        <v>1365.2</v>
+        <v>1357.9</v>
       </c>
       <c r="BL23" t="n">
-        <v>1365.2</v>
+        <v>1357.9</v>
       </c>
       <c r="BM23" t="n">
-        <v>1365.2</v>
+        <v>1357.9</v>
       </c>
       <c r="BN23" t="n">
-        <v>1365.2</v>
+        <v>1357.9</v>
       </c>
       <c r="BO23" t="n">
-        <v>1365.2</v>
+        <v>1357.9</v>
       </c>
       <c r="BP23" t="n">
-        <v>1365.2</v>
+        <v>1357.9</v>
       </c>
       <c r="BQ23" t="n">
-        <v>1365.2</v>
+        <v>1357.9</v>
       </c>
       <c r="BR23" t="n">
-        <v>1365.2</v>
+        <v>1357.9</v>
       </c>
       <c r="BS23" t="n">
-        <v>1365.2</v>
+        <v>1357.9</v>
       </c>
       <c r="BT23" t="n">
-        <v>1365.2</v>
+        <v>1357.9</v>
       </c>
       <c r="BU23" t="n">
-        <v>1365.2</v>
+        <v>1357.9</v>
       </c>
       <c r="BV23" t="n">
-        <v>1365.2</v>
+        <v>1357.9</v>
       </c>
       <c r="BW23" t="n">
-        <v>1365.2</v>
+        <v>1357.9</v>
       </c>
       <c r="BX23" t="n">
-        <v>1365.2</v>
+        <v>1357.9</v>
       </c>
       <c r="BY23" t="n">
-        <v>1365.2</v>
+        <v>1357.9</v>
       </c>
       <c r="BZ23" t="n">
-        <v>1365.2</v>
+        <v>1357.9</v>
       </c>
     </row>
     <row r="24">
@@ -38556,235 +38556,235 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>424</v>
+        <v>419.1</v>
       </c>
       <c r="C24" t="n">
-        <v>432.6</v>
+        <v>427.8</v>
       </c>
       <c r="D24" t="n">
-        <v>442.8</v>
+        <v>438</v>
       </c>
       <c r="E24" t="n">
-        <v>453.1</v>
+        <v>448.3</v>
       </c>
       <c r="F24" t="n">
-        <v>463.6</v>
+        <v>458.8</v>
       </c>
       <c r="G24" t="n">
-        <v>474.3</v>
+        <v>469.5</v>
       </c>
       <c r="H24" t="n">
-        <v>483.3</v>
+        <v>478.5</v>
       </c>
       <c r="I24" t="n">
-        <v>494.3</v>
+        <v>489.4</v>
       </c>
       <c r="J24" t="n">
-        <v>505.4</v>
+        <v>500.6</v>
       </c>
       <c r="K24" t="n">
-        <v>511.2</v>
+        <v>506.3</v>
       </c>
       <c r="L24" t="n">
-        <v>528.5</v>
+        <v>523.7</v>
       </c>
       <c r="M24" t="n">
-        <v>538.3</v>
+        <v>533.4</v>
       </c>
       <c r="N24" t="n">
-        <v>550.6</v>
+        <v>545.7</v>
       </c>
       <c r="O24" t="n">
-        <v>563.4</v>
+        <v>558.5</v>
       </c>
       <c r="P24" t="n">
-        <v>576.6</v>
+        <v>571.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>590.5</v>
+        <v>585.6</v>
       </c>
       <c r="R24" t="n">
-        <v>602</v>
+        <v>597.1</v>
       </c>
       <c r="S24" t="n">
-        <v>612.3</v>
+        <v>607.4</v>
       </c>
       <c r="T24" t="n">
-        <v>623.1</v>
+        <v>618.2</v>
       </c>
       <c r="U24" t="n">
-        <v>634.2</v>
+        <v>629.3</v>
       </c>
       <c r="V24" t="n">
-        <v>645.6</v>
+        <v>640.8</v>
       </c>
       <c r="W24" t="n">
-        <v>657.5</v>
+        <v>652.7</v>
       </c>
       <c r="X24" t="n">
-        <v>669.8</v>
+        <v>664.9</v>
       </c>
       <c r="Y24" t="n">
-        <v>682.5</v>
+        <v>677.6</v>
       </c>
       <c r="Z24" t="n">
-        <v>695.6</v>
+        <v>690.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>709.2</v>
+        <v>704.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>723.3</v>
+        <v>718.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>737.9</v>
+        <v>733.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>753.1</v>
+        <v>748.2</v>
       </c>
       <c r="AE24" t="n">
-        <v>768.8</v>
+        <v>763.9</v>
       </c>
       <c r="AF24" t="n">
-        <v>785</v>
+        <v>780.2</v>
       </c>
       <c r="AG24" t="n">
-        <v>801.9</v>
+        <v>797</v>
       </c>
       <c r="AH24" t="n">
-        <v>819.3</v>
+        <v>814.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>837.5</v>
+        <v>832.6</v>
       </c>
       <c r="AJ24" t="n">
-        <v>856.1</v>
+        <v>851.2</v>
       </c>
       <c r="AK24" t="n">
-        <v>875.1</v>
+        <v>870.3</v>
       </c>
       <c r="AL24" t="n">
-        <v>894.7</v>
+        <v>889.8</v>
       </c>
       <c r="AM24" t="n">
-        <v>914.7</v>
+        <v>909.8</v>
       </c>
       <c r="AN24" t="n">
-        <v>935.1</v>
+        <v>930.3</v>
       </c>
       <c r="AO24" t="n">
-        <v>983.1</v>
+        <v>978.3</v>
       </c>
       <c r="AP24" t="n">
-        <v>1032.2</v>
+        <v>1027.4</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1082.5</v>
+        <v>1077.7</v>
       </c>
       <c r="AR24" t="n">
-        <v>1134</v>
+        <v>1129.2</v>
       </c>
       <c r="AS24" t="n">
-        <v>1186.7</v>
+        <v>1181.9</v>
       </c>
       <c r="AT24" t="n">
-        <v>1240.7</v>
+        <v>1235.9</v>
       </c>
       <c r="AU24" t="n">
-        <v>1385.2</v>
+        <v>1380.4</v>
       </c>
       <c r="AV24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
       <c r="AW24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
       <c r="AX24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
       <c r="AY24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
       <c r="BA24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
       <c r="BB24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
       <c r="BC24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
       <c r="BD24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
       <c r="BE24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
       <c r="BF24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
       <c r="BG24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
       <c r="BH24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
       <c r="BI24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
       <c r="BJ24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
       <c r="BK24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
       <c r="BL24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
       <c r="BM24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
       <c r="BN24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
       <c r="BO24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
       <c r="BP24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
       <c r="BR24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
       <c r="BS24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
       <c r="BT24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
       <c r="BU24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
       <c r="BV24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
       <c r="BW24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
       <c r="BX24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
       <c r="BY24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
       <c r="BZ24" t="n">
-        <v>1585.1</v>
+        <v>1580.2</v>
       </c>
     </row>
     <row r="25">
@@ -38794,235 +38794,235 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="C25" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="D25" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="E25" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="F25" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="G25" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="H25" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="J25" t="n">
         <v>19.1</v>
       </c>
-      <c r="C25" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="D25" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="E25" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="F25" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="G25" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="H25" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="I25" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>22.6</v>
-      </c>
       <c r="K25" t="n">
-        <v>22.9</v>
+        <v>19.3</v>
       </c>
       <c r="L25" t="n">
-        <v>23.6</v>
+        <v>20.1</v>
       </c>
       <c r="M25" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="N25" t="n">
+        <v>21</v>
+      </c>
+      <c r="O25" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="P25" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="R25" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="S25" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="T25" t="n">
         <v>24.1</v>
       </c>
-      <c r="N25" t="n">
+      <c r="U25" t="n">
         <v>24.6</v>
       </c>
-      <c r="O25" t="n">
+      <c r="V25" t="n">
         <v>25.1</v>
       </c>
-      <c r="P25" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="R25" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="S25" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="U25" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="V25" t="n">
-        <v>28.7</v>
-      </c>
       <c r="W25" t="n">
-        <v>29.2</v>
+        <v>25.6</v>
       </c>
       <c r="X25" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="AD25" t="n">
         <v>29.7</v>
       </c>
-      <c r="Y25" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>32</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>33.3</v>
-      </c>
       <c r="AE25" t="n">
-        <v>42.8</v>
+        <v>39.2</v>
       </c>
       <c r="AF25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="AG25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="AH25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="AI25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="AK25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="AL25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="AM25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="AN25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="AO25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="AP25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="AQ25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="AR25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="AS25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="AT25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="AU25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="AV25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="AW25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="AX25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="AY25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="AZ25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="BA25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="BB25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="BC25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="BD25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="BE25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="BF25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="BG25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="BH25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="BI25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="BJ25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="BK25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="BL25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="BM25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="BN25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="BO25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="BP25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="BQ25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="BR25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="BS25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="BT25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="BU25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="BV25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="BW25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="BX25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="BY25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
       <c r="BZ25" t="n">
-        <v>49.6</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="26">
@@ -39032,235 +39032,235 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7.3</v>
+        <v>8.4</v>
       </c>
       <c r="C26" t="n">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="D26" t="n">
-        <v>7.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>8</v>
+        <v>9.1</v>
       </c>
       <c r="F26" t="n">
-        <v>8.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>8.5</v>
+        <v>9.6</v>
       </c>
       <c r="H26" t="n">
-        <v>8.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>8.9</v>
+        <v>10</v>
       </c>
       <c r="J26" t="n">
-        <v>9.199999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="K26" t="n">
-        <v>9.300000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="L26" t="n">
-        <v>9.699999999999999</v>
+        <v>10.8</v>
       </c>
       <c r="M26" t="n">
-        <v>9.9</v>
+        <v>11</v>
       </c>
       <c r="N26" t="n">
-        <v>10.2</v>
+        <v>11.3</v>
       </c>
       <c r="O26" t="n">
-        <v>10.5</v>
+        <v>11.6</v>
       </c>
       <c r="P26" t="n">
-        <v>10.8</v>
+        <v>11.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="R26" t="n">
-        <v>11.4</v>
+        <v>12.5</v>
       </c>
       <c r="S26" t="n">
-        <v>11.7</v>
+        <v>12.7</v>
       </c>
       <c r="T26" t="n">
-        <v>11.9</v>
+        <v>13</v>
       </c>
       <c r="U26" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="V26" t="n">
-        <v>12.4</v>
+        <v>13.5</v>
       </c>
       <c r="W26" t="n">
-        <v>12.7</v>
+        <v>13.8</v>
       </c>
       <c r="X26" t="n">
-        <v>13</v>
+        <v>14.1</v>
       </c>
       <c r="Y26" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="Z26" t="n">
-        <v>13.6</v>
+        <v>14.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>13.9</v>
+        <v>15</v>
       </c>
       <c r="AB26" t="n">
-        <v>14.2</v>
+        <v>15.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>14.6</v>
+        <v>15.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>14.9</v>
+        <v>16</v>
       </c>
       <c r="AE26" t="n">
-        <v>15.3</v>
+        <v>16.4</v>
       </c>
       <c r="AF26" t="n">
-        <v>15.7</v>
+        <v>16.7</v>
       </c>
       <c r="AG26" t="n">
-        <v>16</v>
+        <v>17.1</v>
       </c>
       <c r="AH26" t="n">
-        <v>16.4</v>
+        <v>17.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>16.9</v>
+        <v>18</v>
       </c>
       <c r="AJ26" t="n">
-        <v>17.3</v>
+        <v>18.4</v>
       </c>
       <c r="AK26" t="n">
-        <v>17.7</v>
+        <v>18.8</v>
       </c>
       <c r="AL26" t="n">
-        <v>18.2</v>
+        <v>19.3</v>
       </c>
       <c r="AM26" t="n">
-        <v>18.7</v>
+        <v>19.7</v>
       </c>
       <c r="AN26" t="n">
-        <v>133.8</v>
+        <v>134.9</v>
       </c>
       <c r="AO26" t="n">
-        <v>251.7</v>
+        <v>252.8</v>
       </c>
       <c r="AP26" t="n">
-        <v>372.5</v>
+        <v>373.6</v>
       </c>
       <c r="AQ26" t="n">
-        <v>496.1</v>
+        <v>497.2</v>
       </c>
       <c r="AR26" t="n">
-        <v>622.8</v>
+        <v>623.9</v>
       </c>
       <c r="AS26" t="n">
-        <v>752.4</v>
+        <v>753.5</v>
       </c>
       <c r="AT26" t="n">
-        <v>885.2</v>
+        <v>886.3</v>
       </c>
       <c r="AU26" t="n">
-        <v>1235.5</v>
+        <v>1236.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
       <c r="AW26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
       <c r="AX26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
       <c r="AY26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
       <c r="BA26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
       <c r="BB26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
       <c r="BC26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
       <c r="BD26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
       <c r="BE26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
       <c r="BF26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
       <c r="BG26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
       <c r="BH26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
       <c r="BI26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
       <c r="BJ26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
       <c r="BK26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
       <c r="BL26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
       <c r="BM26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
       <c r="BN26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
       <c r="BO26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
       <c r="BP26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
       <c r="BQ26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
       <c r="BR26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
       <c r="BS26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
       <c r="BT26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
       <c r="BU26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
       <c r="BV26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
       <c r="BW26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
       <c r="BX26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
       <c r="BY26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
       <c r="BZ26" t="n">
-        <v>1467.8</v>
+        <v>1468.9</v>
       </c>
     </row>
   </sheetData>

--- a/W13/analysis/W13_growth_by_settlement.xlsx
+++ b/W13/analysis/W13_growth_by_settlement.xlsx
@@ -17,6 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workbook projection" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overflow routes" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Five-year to saturation" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Five-year Qadf" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Occupancy" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1519,7 +1522,6 @@
       <c r="F19" t="n">
         <v>0</v>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>24</v>
       </c>
@@ -2056,6 +2058,2974 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Settlement</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>2035</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>2045</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>2060</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>2065</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>2075</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Saturation year</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>IBRI</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>67094</v>
+      </c>
+      <c r="C2" t="n">
+        <v>68702</v>
+      </c>
+      <c r="D2" t="n">
+        <v>78086</v>
+      </c>
+      <c r="E2" t="n">
+        <v>88257</v>
+      </c>
+      <c r="F2" t="n">
+        <v>100049</v>
+      </c>
+      <c r="G2" t="n">
+        <v>110330</v>
+      </c>
+      <c r="H2" t="n">
+        <v>122514</v>
+      </c>
+      <c r="I2" t="n">
+        <v>137057</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AD DARIZ</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>11852</v>
+      </c>
+      <c r="C3" t="n">
+        <v>12136</v>
+      </c>
+      <c r="D3" t="n">
+        <v>13794</v>
+      </c>
+      <c r="E3" t="n">
+        <v>15590</v>
+      </c>
+      <c r="F3" t="n">
+        <v>17673</v>
+      </c>
+      <c r="G3" t="n">
+        <v>19490</v>
+      </c>
+      <c r="H3" t="n">
+        <v>21642</v>
+      </c>
+      <c r="I3" t="n">
+        <v>24211</v>
+      </c>
+      <c r="J3" t="n">
+        <v>27246</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AL ARAQI</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>10698</v>
+      </c>
+      <c r="C4" t="n">
+        <v>10954</v>
+      </c>
+      <c r="D4" t="n">
+        <v>12451</v>
+      </c>
+      <c r="E4" t="n">
+        <v>14072</v>
+      </c>
+      <c r="F4" t="n">
+        <v>15953</v>
+      </c>
+      <c r="G4" t="n">
+        <v>17592</v>
+      </c>
+      <c r="H4" t="n">
+        <v>19535</v>
+      </c>
+      <c r="I4" t="n">
+        <v>21854</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AL AYNAYN</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4553</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4662</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5299</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5989</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6789</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7487</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8314</v>
+      </c>
+      <c r="I5" t="n">
+        <v>9301</v>
+      </c>
+      <c r="J5" t="n">
+        <v>12012</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AL WAHRAH</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3351</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3431</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3900</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4408</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4997</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5510</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6119</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6845</v>
+      </c>
+      <c r="J6" t="n">
+        <v>7703</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8684</v>
+      </c>
+      <c r="L6" t="n">
+        <v>9803</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>2071</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AT TAYYIB</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3349</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3429</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3898</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4405</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4994</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5507</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6115</v>
+      </c>
+      <c r="I7" t="n">
+        <v>6841</v>
+      </c>
+      <c r="J7" t="n">
+        <v>8131</v>
+      </c>
+      <c r="K7" t="n">
+        <v>17539</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AD DIBAYSHI</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2724</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2789</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3170</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3583</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4062</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4479</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4974</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5564</v>
+      </c>
+      <c r="J8" t="n">
+        <v>6262</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>2063</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AL JIBAYYAH</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2684</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2749</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3128</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3538</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4014</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4429</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4921</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5508</v>
+      </c>
+      <c r="J9" t="n">
+        <v>6201</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6985</v>
+      </c>
+      <c r="L9" t="n">
+        <v>8694</v>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BAT</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2558</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2619</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2977</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3365</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3814</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4206</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4671</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TANAM</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2116</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2167</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2463</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2783</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3155</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3480</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3864</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4322</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4864</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5961</v>
+      </c>
+      <c r="L11" t="n">
+        <v>8895</v>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SAYH AL MASARRAT</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1828</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1872</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2127</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2405</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2726</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3006</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3338</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3734</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4202</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4750</v>
+      </c>
+      <c r="L12" t="n">
+        <v>6229</v>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SUWAYDA AL MA</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1559</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1596</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1814</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2051</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2325</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2564</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2847</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3185</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3584</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4035</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4543</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>2073</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HIJAR</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1408</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1442</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1639</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1852</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2315</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2571</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AL JAHLI</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1376</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1409</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1601</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1810</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2052</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2263</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2513</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2811</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3163</v>
+      </c>
+      <c r="K15" t="n">
+        <v>8264</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AL GHUBAYRAH</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>644</v>
+      </c>
+      <c r="C16" t="n">
+        <v>659</v>
+      </c>
+      <c r="D16" t="n">
+        <v>750</v>
+      </c>
+      <c r="E16" t="n">
+        <v>847</v>
+      </c>
+      <c r="F16" t="n">
+        <v>960</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1059</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1176</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1756</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2576</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3502</v>
+      </c>
+      <c r="L16" t="n">
+        <v>4546</v>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>2071</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AL QURAYN</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>588</v>
+      </c>
+      <c r="C17" t="n">
+        <v>602</v>
+      </c>
+      <c r="D17" t="n">
+        <v>684</v>
+      </c>
+      <c r="E17" t="n">
+        <v>773</v>
+      </c>
+      <c r="F17" t="n">
+        <v>877</v>
+      </c>
+      <c r="G17" t="n">
+        <v>967</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1074</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1201</v>
+      </c>
+      <c r="J17" t="n">
+        <v>8376</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AL AKHEEDAR</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>480</v>
+      </c>
+      <c r="C18" t="n">
+        <v>492</v>
+      </c>
+      <c r="D18" t="n">
+        <v>559</v>
+      </c>
+      <c r="E18" t="n">
+        <v>631</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AL MAKHTIBYAH</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>364</v>
+      </c>
+      <c r="C19" t="n">
+        <v>373</v>
+      </c>
+      <c r="D19" t="n">
+        <v>424</v>
+      </c>
+      <c r="E19" t="n">
+        <v>479</v>
+      </c>
+      <c r="F19" t="n">
+        <v>543</v>
+      </c>
+      <c r="G19" t="n">
+        <v>599</v>
+      </c>
+      <c r="H19" t="n">
+        <v>665</v>
+      </c>
+      <c r="I19" t="n">
+        <v>744</v>
+      </c>
+      <c r="J19" t="n">
+        <v>837</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1140</v>
+      </c>
+      <c r="L19" t="n">
+        <v>5288</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AL QALI</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>224</v>
+      </c>
+      <c r="C20" t="n">
+        <v>229</v>
+      </c>
+      <c r="D20" t="n">
+        <v>261</v>
+      </c>
+      <c r="E20" t="n">
+        <v>295</v>
+      </c>
+      <c r="F20" t="n">
+        <v>366</v>
+      </c>
+      <c r="G20" t="n">
+        <v>474</v>
+      </c>
+      <c r="H20" t="n">
+        <v>602</v>
+      </c>
+      <c r="I20" t="n">
+        <v>851</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1415</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SATWAH</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>165</v>
+      </c>
+      <c r="C21" t="n">
+        <v>169</v>
+      </c>
+      <c r="D21" t="n">
+        <v>192</v>
+      </c>
+      <c r="E21" t="n">
+        <v>217</v>
+      </c>
+      <c r="F21" t="n">
+        <v>246</v>
+      </c>
+      <c r="G21" t="n">
+        <v>271</v>
+      </c>
+      <c r="H21" t="n">
+        <v>301</v>
+      </c>
+      <c r="I21" t="n">
+        <v>337</v>
+      </c>
+      <c r="J21" t="n">
+        <v>625</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SHALASHIL</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>152</v>
+      </c>
+      <c r="C22" t="n">
+        <v>156</v>
+      </c>
+      <c r="D22" t="n">
+        <v>177</v>
+      </c>
+      <c r="E22" t="n">
+        <v>200</v>
+      </c>
+      <c r="F22" t="n">
+        <v>227</v>
+      </c>
+      <c r="G22" t="n">
+        <v>250</v>
+      </c>
+      <c r="H22" t="n">
+        <v>278</v>
+      </c>
+      <c r="I22" t="n">
+        <v>311</v>
+      </c>
+      <c r="J22" t="n">
+        <v>7004</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>USAYBUQ</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>91</v>
+      </c>
+      <c r="C23" t="n">
+        <v>93</v>
+      </c>
+      <c r="D23" t="n">
+        <v>106</v>
+      </c>
+      <c r="E23" t="n">
+        <v>120</v>
+      </c>
+      <c r="F23" t="n">
+        <v>136</v>
+      </c>
+      <c r="G23" t="n">
+        <v>150</v>
+      </c>
+      <c r="H23" t="n">
+        <v>166</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="n">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>WADI AL MANKAS</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>49</v>
+      </c>
+      <c r="C24" t="n">
+        <v>50</v>
+      </c>
+      <c r="D24" t="n">
+        <v>57</v>
+      </c>
+      <c r="E24" t="n">
+        <v>64</v>
+      </c>
+      <c r="F24" t="n">
+        <v>73</v>
+      </c>
+      <c r="G24" t="n">
+        <v>81</v>
+      </c>
+      <c r="H24" t="n">
+        <v>89</v>
+      </c>
+      <c r="I24" t="n">
+        <v>100</v>
+      </c>
+      <c r="J24" t="n">
+        <v>113</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2903</v>
+      </c>
+      <c r="L24" t="n">
+        <v>8576</v>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="n">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ASH SHIAB</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>47</v>
+      </c>
+      <c r="C25" t="n">
+        <v>48</v>
+      </c>
+      <c r="D25" t="n">
+        <v>55</v>
+      </c>
+      <c r="E25" t="n">
+        <v>62</v>
+      </c>
+      <c r="F25" t="n">
+        <v>70</v>
+      </c>
+      <c r="G25" t="n">
+        <v>77</v>
+      </c>
+      <c r="H25" t="n">
+        <v>86</v>
+      </c>
+      <c r="I25" t="n">
+        <v>96</v>
+      </c>
+      <c r="J25" t="n">
+        <v>107</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="n">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MIAYRID</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>24</v>
+      </c>
+      <c r="C26" t="n">
+        <v>24</v>
+      </c>
+      <c r="D26" t="n">
+        <v>24</v>
+      </c>
+      <c r="E26" t="n">
+        <v>24</v>
+      </c>
+      <c r="F26" t="n">
+        <v>24</v>
+      </c>
+      <c r="G26" t="n">
+        <v>24</v>
+      </c>
+      <c r="H26" t="n">
+        <v>24</v>
+      </c>
+      <c r="I26" t="n">
+        <v>24</v>
+      </c>
+      <c r="J26" t="n">
+        <v>24</v>
+      </c>
+      <c r="K26" t="n">
+        <v>24</v>
+      </c>
+      <c r="L26" t="n">
+        <v>24</v>
+      </c>
+      <c r="M26" t="n">
+        <v>24</v>
+      </c>
+      <c r="N26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>119978</v>
+      </c>
+      <c r="C27" t="n">
+        <v>122852</v>
+      </c>
+      <c r="D27" t="n">
+        <v>139636</v>
+      </c>
+      <c r="E27" t="n">
+        <v>157820</v>
+      </c>
+      <c r="F27" t="n">
+        <v>178909</v>
+      </c>
+      <c r="G27" t="n">
+        <v>197294</v>
+      </c>
+      <c r="H27" t="n">
+        <v>219083</v>
+      </c>
+      <c r="I27" t="n">
+        <v>245087</v>
+      </c>
+      <c r="J27" t="n">
+        <v>275803</v>
+      </c>
+      <c r="K27" t="n">
+        <v>310526</v>
+      </c>
+      <c r="L27" t="n">
+        <v>349622</v>
+      </c>
+      <c r="M27" t="n">
+        <v>367649</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2073</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Settlement</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>2035</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>2045</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>2060</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>2065</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>2075</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Saturation year</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>IBRI</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>11492.4</v>
+      </c>
+      <c r="C2" t="n">
+        <v>11767.7</v>
+      </c>
+      <c r="D2" t="n">
+        <v>13375.1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>15117.2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>17136.9</v>
+      </c>
+      <c r="G2" t="n">
+        <v>18897.8</v>
+      </c>
+      <c r="H2" t="n">
+        <v>20984.8</v>
+      </c>
+      <c r="I2" t="n">
+        <v>23475.8</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AD DARIZ</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2078.6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2362.6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2670.3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3027.1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3338.1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3706.8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4146.8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4666.7</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AL ARAQI</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1832.3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1876.2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2132.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2410.3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2732.3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3013.1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3345.9</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3743</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AL AYNAYN</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>779.8</v>
+      </c>
+      <c r="C5" t="n">
+        <v>798.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>907.6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1025.8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1162.9</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1282.4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1424</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1593</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2057.4</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AL WAHRAH</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>573.9</v>
+      </c>
+      <c r="C6" t="n">
+        <v>587.7</v>
+      </c>
+      <c r="D6" t="n">
+        <v>668</v>
+      </c>
+      <c r="E6" t="n">
+        <v>755</v>
+      </c>
+      <c r="F6" t="n">
+        <v>855.9</v>
+      </c>
+      <c r="G6" t="n">
+        <v>943.8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1048</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1172.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1319.4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1487.4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1679</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>2071</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AT TAYYIB</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>799.4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>813.2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>893.4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>980.4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1081.2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1169.1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1273.3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1397.6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1618.5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3229.9</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AD DIBAYSHI</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>480.9</v>
+      </c>
+      <c r="C8" t="n">
+        <v>492.1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>557.4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>628.1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>710.1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>781.6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>866.3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>967.4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1086.9</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>2063</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AL JIBAYYAH</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>459.7</v>
+      </c>
+      <c r="C9" t="n">
+        <v>470.9</v>
+      </c>
+      <c r="D9" t="n">
+        <v>535.7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>606</v>
+      </c>
+      <c r="F9" t="n">
+        <v>687.6</v>
+      </c>
+      <c r="G9" t="n">
+        <v>758.6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>842.9</v>
+      </c>
+      <c r="I9" t="n">
+        <v>943.4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1062.2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1196.4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1489.2</v>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BAT</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>438.1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>448.6</v>
+      </c>
+      <c r="D10" t="n">
+        <v>509.8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>576.3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>653.3</v>
+      </c>
+      <c r="G10" t="n">
+        <v>720.4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>800</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TANAM</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>419.1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>427.8</v>
+      </c>
+      <c r="D11" t="n">
+        <v>478.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>533.4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>597.1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>652.7</v>
+      </c>
+      <c r="H11" t="n">
+        <v>718.5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>797</v>
+      </c>
+      <c r="J11" t="n">
+        <v>889.8</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1077.7</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1580.2</v>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SAYH AL MASARRAT</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>313.1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>320.6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>364.4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>411.9</v>
+      </c>
+      <c r="F12" t="n">
+        <v>466.9</v>
+      </c>
+      <c r="G12" t="n">
+        <v>514.9</v>
+      </c>
+      <c r="H12" t="n">
+        <v>571.7</v>
+      </c>
+      <c r="I12" t="n">
+        <v>639.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>719.8</v>
+      </c>
+      <c r="K12" t="n">
+        <v>813.6</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1066.9</v>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SUWAYDA AL MA</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>267</v>
+      </c>
+      <c r="C13" t="n">
+        <v>273.4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>310.8</v>
+      </c>
+      <c r="E13" t="n">
+        <v>351.2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>398.2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>439.1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>487.6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>545.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>613.8</v>
+      </c>
+      <c r="K13" t="n">
+        <v>691.1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>778.1</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>2073</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HIJAR</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>241.2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>246.9</v>
+      </c>
+      <c r="D14" t="n">
+        <v>280.7</v>
+      </c>
+      <c r="E14" t="n">
+        <v>317.2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>359.6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>396.6</v>
+      </c>
+      <c r="H14" t="n">
+        <v>440.4</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AL JAHLI</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>235.7</v>
+      </c>
+      <c r="C15" t="n">
+        <v>241.3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>274.3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>310</v>
+      </c>
+      <c r="F15" t="n">
+        <v>351.4</v>
+      </c>
+      <c r="G15" t="n">
+        <v>387.6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>430.4</v>
+      </c>
+      <c r="I15" t="n">
+        <v>481.4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>541.8</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1415.5</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AL GHUBAYRAH</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="D16" t="n">
+        <v>128.4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>145.1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>164.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="H16" t="n">
+        <v>201.4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>300.8</v>
+      </c>
+      <c r="J16" t="n">
+        <v>441.2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>599.9</v>
+      </c>
+      <c r="L16" t="n">
+        <v>778.6</v>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>2071</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AL QURAYN</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="C17" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>150.2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>165.6</v>
+      </c>
+      <c r="H17" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="I17" t="n">
+        <v>205.7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1434.7</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AL AKHEEDAR</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="E18" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AL MAKHTIBYAH</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="C19" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="D19" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="E19" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="G19" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="H19" t="n">
+        <v>133.1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>146.7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>162.6</v>
+      </c>
+      <c r="K19" t="n">
+        <v>214.6</v>
+      </c>
+      <c r="L19" t="n">
+        <v>925</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AL QALI</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="C20" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="E20" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="G20" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>103</v>
+      </c>
+      <c r="I20" t="n">
+        <v>145.8</v>
+      </c>
+      <c r="J20" t="n">
+        <v>242.4</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SATWAH</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>29</v>
+      </c>
+      <c r="D21" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="E21" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="I21" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>107</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SHALASHIL</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>26</v>
+      </c>
+      <c r="C22" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="D22" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="G22" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="I22" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1199.7</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>USAYBUQ</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="C23" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="D23" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="H23" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="n">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>WADI AL MANKAS</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="C24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="E24" t="n">
+        <v>11</v>
+      </c>
+      <c r="F24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="H24" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="I24" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="K24" t="n">
+        <v>497.2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1468.9</v>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="n">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ASH SHIAB</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>8</v>
+      </c>
+      <c r="C25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="D25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="E25" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="F25" t="n">
+        <v>12</v>
+      </c>
+      <c r="G25" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="I25" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="n">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MIAYRID</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>20866</v>
+      </c>
+      <c r="C27" t="n">
+        <v>21359</v>
+      </c>
+      <c r="D27" t="n">
+        <v>24233</v>
+      </c>
+      <c r="E27" t="n">
+        <v>27348</v>
+      </c>
+      <c r="F27" t="n">
+        <v>30960</v>
+      </c>
+      <c r="G27" t="n">
+        <v>34109</v>
+      </c>
+      <c r="H27" t="n">
+        <v>37841</v>
+      </c>
+      <c r="I27" t="n">
+        <v>42295</v>
+      </c>
+      <c r="J27" t="n">
+        <v>47556</v>
+      </c>
+      <c r="K27" t="n">
+        <v>53504</v>
+      </c>
+      <c r="L27" t="n">
+        <v>60200</v>
+      </c>
+      <c r="M27" t="n">
+        <v>63288</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2073</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SETTLE</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>properties</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>workbook_2024</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>OR_raw</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>OR_used</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>people_used</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>delta_vs_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>IBRI</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>11052</v>
+      </c>
+      <c r="C2" t="n">
+        <v>67105.50878491651</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="F2" t="n">
+        <v>58663</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-8443</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AD DARIZ</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2439</v>
+      </c>
+      <c r="C3" t="n">
+        <v>11849.67146371732</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="F3" t="n">
+        <v>12937</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AL ARAQI</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2466</v>
+      </c>
+      <c r="C4" t="n">
+        <v>10695.67732032832</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="F4" t="n">
+        <v>13087</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2391</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AL AYNAYN</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>889</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4554.030567590516</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4716</v>
+      </c>
+      <c r="G5" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AL WAHRAH</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>716</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3351.079096906229</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3799</v>
+      </c>
+      <c r="G6" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AT TAYYIB</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>833</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3348.081709520803</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4418</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AL JIBAYYAH</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>524</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2685.659097341665</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2780</v>
+      </c>
+      <c r="G8" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BAT</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>418</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2556.771439768348</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2218</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-339</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AD DIBAYSHI</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>681</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2410.898587010952</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3613</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TANAM</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>403</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2116.155494110731</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2140</v>
+      </c>
+      <c r="G11" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SUWAYDA AL MA</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>301</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1558.641440421502</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1598</v>
+      </c>
+      <c r="G12" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>HIJAR</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>352</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1033.099518843483</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1868</v>
+      </c>
+      <c r="G13" t="n">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AL GHUBAYRAH</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>161</v>
+      </c>
+      <c r="C14" t="n">
+        <v>631.4496091964032</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>854</v>
+      </c>
+      <c r="G14" t="n">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AL QURAYN</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>147</v>
+      </c>
+      <c r="C15" t="n">
+        <v>548.5218915329516</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>779</v>
+      </c>
+      <c r="G15" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SAYH AL MASARRAT</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>457</v>
+      </c>
+      <c r="C16" t="n">
+        <v>465.5941738694999</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2429</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AL JAHLI</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>344</v>
+      </c>
+      <c r="C17" t="n">
+        <v>414.6385883172585</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1828</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SATWAH</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>27</v>
+      </c>
+      <c r="C18" t="n">
+        <v>262.7709607890096</v>
+      </c>
+      <c r="D18" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="E18" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="F18" t="n">
+        <v>143</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-120</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AL AKHEEDAR</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>120</v>
+      </c>
+      <c r="C19" t="n">
+        <v>197.8275674381137</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" t="n">
+        <v>638</v>
+      </c>
+      <c r="G19" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AL QALI</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>56</v>
+      </c>
+      <c r="C20" t="n">
+        <v>190.8336635387865</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" t="n">
+        <v>297</v>
+      </c>
+      <c r="G20" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SHALASHIL</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>38</v>
+      </c>
+      <c r="C21" t="n">
+        <v>129.8867867017918</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" t="n">
+        <v>202</v>
+      </c>
+      <c r="G21" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AL MAKHTIBYAH</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>91</v>
+      </c>
+      <c r="C22" t="n">
+        <v>121.8937536739892</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" t="n">
+        <v>483</v>
+      </c>
+      <c r="G22" t="n">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>USAYBUQ</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>21</v>
+      </c>
+      <c r="C23" t="n">
+        <v>90.92075069125428</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="F23" t="n">
+        <v>111</v>
+      </c>
+      <c r="G23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>WADI AL MANKAS</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>8</v>
+      </c>
+      <c r="C24" t="n">
+        <v>51.95471468071673</v>
+      </c>
+      <c r="D24" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="E24" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="F24" t="n">
+        <v>42</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ASH SHIAB</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>11</v>
+      </c>
+      <c r="C25" t="n">
+        <v>46.95906903834011</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="F25" t="n">
+        <v>58</v>
+      </c>
+      <c r="G25" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MIAYRID</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="n">
+        <v>33.97039036816093</v>
+      </c>
+      <c r="D26" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="E26" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="F26" t="n">
+        <v>21</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
